--- a/002/002_REACCIONES_BASES_3.0.xlsx
+++ b/002/002_REACCIONES_BASES_3.0.xlsx
@@ -1893,22 +1893,22 @@
         </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>0.501</v>
+        <v>0.499</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0.763</v>
+        <v>0.759</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.106</v>
+        <v>0.105</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.081</v>
+        <v>0.08</v>
       </c>
       <c r="H46" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>1.911</v>
+        <v>1.904</v>
       </c>
     </row>
     <row r="47">
@@ -1926,22 +1926,22 @@
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>0.21</v>
+        <v>0.209</v>
       </c>
       <c r="E47" s="5" t="n">
         <v>0.107</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.174</v>
+        <v>0.172</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.107</v>
+        <v>0.106</v>
       </c>
       <c r="H47" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>1.321</v>
+        <v>1.316</v>
       </c>
     </row>
     <row r="48">
@@ -1959,22 +1959,22 @@
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>0.268</v>
+        <v>0.267</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0.145</v>
+        <v>0.143</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0.198</v>
+        <v>0.196</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.116</v>
+        <v>0.115</v>
       </c>
       <c r="H48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>1.69</v>
+        <v>1.682</v>
       </c>
     </row>
     <row r="49">
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>0.644</v>
+        <v>0.642</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0.764</v>
+        <v>0.76</v>
       </c>
       <c r="F49" s="5" t="n">
         <v>0.105</v>
@@ -2007,7 +2007,7 @@
         <v>0</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>1.946</v>
+        <v>1.939</v>
       </c>
     </row>
     <row r="50">
@@ -2025,22 +2025,22 @@
         </is>
       </c>
       <c r="D50" s="5" t="n">
-        <v>0.21</v>
+        <v>0.209</v>
       </c>
       <c r="E50" s="5" t="n">
         <v>0.107</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.174</v>
+        <v>0.173</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.107</v>
+        <v>0.106</v>
       </c>
       <c r="H50" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>1.321</v>
+        <v>1.316</v>
       </c>
     </row>
     <row r="51">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>0.268</v>
+        <v>0.267</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0.145</v>
+        <v>0.144</v>
       </c>
       <c r="F51" s="5" t="n">
         <v>0.197</v>
@@ -2073,7 +2073,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>1.69</v>
+        <v>1.682</v>
       </c>
     </row>
     <row r="52">
@@ -2553,22 +2553,22 @@
         </is>
       </c>
       <c r="D66" s="5" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0.458</v>
+        <v>0.455</v>
       </c>
       <c r="F66" s="5" t="n">
         <v>0.222</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.222</v>
+        <v>0.223</v>
       </c>
       <c r="H66" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>0.006</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="67">
@@ -2595,7 +2595,7 @@
         <v>0.342</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.268</v>
+        <v>0.269</v>
       </c>
       <c r="H67" s="5" t="n">
         <v>0</v>
@@ -2619,22 +2619,22 @@
         </is>
       </c>
       <c r="D68" s="5" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="F68" s="5" t="n">
         <v>0.382</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.284</v>
+        <v>0.285</v>
       </c>
       <c r="H68" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="69">
@@ -2652,22 +2652,22 @@
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>0.46</v>
+        <v>0.454</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>0.223</v>
+        <v>0.22</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.223</v>
+        <v>0.221</v>
       </c>
       <c r="H69" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>0.006</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="70">
@@ -2691,10 +2691,10 @@
         <v>0.023</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>0.344</v>
+        <v>0.339</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.269</v>
+        <v>0.266</v>
       </c>
       <c r="H70" s="5" t="n">
         <v>0</v>
@@ -2721,19 +2721,19 @@
         <v>0.001</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>0.442</v>
+        <v>0.434</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>0.384</v>
+        <v>0.378</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.284</v>
+        <v>0.281</v>
       </c>
       <c r="H71" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="72">
@@ -3213,22 +3213,22 @@
         </is>
       </c>
       <c r="D86" s="5" t="n">
-        <v>-0.501</v>
+        <v>-0.499</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>-0.763</v>
+        <v>-0.759</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>-0.106</v>
+        <v>-0.105</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>-0.081</v>
+        <v>-0.08</v>
       </c>
       <c r="H86" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>-1.911</v>
+        <v>-1.904</v>
       </c>
     </row>
     <row r="87">
@@ -3246,22 +3246,22 @@
         </is>
       </c>
       <c r="D87" s="5" t="n">
-        <v>-0.21</v>
+        <v>-0.209</v>
       </c>
       <c r="E87" s="5" t="n">
         <v>-0.107</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>-0.174</v>
+        <v>-0.172</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>-0.107</v>
+        <v>-0.106</v>
       </c>
       <c r="H87" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>-1.321</v>
+        <v>-1.316</v>
       </c>
     </row>
     <row r="88">
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="D88" s="5" t="n">
-        <v>-0.268</v>
+        <v>-0.267</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>-0.145</v>
+        <v>-0.143</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>-0.198</v>
+        <v>-0.196</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>-0.116</v>
+        <v>-0.115</v>
       </c>
       <c r="H88" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>-1.69</v>
+        <v>-1.682</v>
       </c>
     </row>
     <row r="89">
@@ -3312,10 +3312,10 @@
         </is>
       </c>
       <c r="D89" s="5" t="n">
-        <v>-0.644</v>
+        <v>-0.642</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>-0.764</v>
+        <v>-0.76</v>
       </c>
       <c r="F89" s="5" t="n">
         <v>-0.105</v>
@@ -3327,7 +3327,7 @@
         <v>-0</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>-1.946</v>
+        <v>-1.939</v>
       </c>
     </row>
     <row r="90">
@@ -3345,22 +3345,22 @@
         </is>
       </c>
       <c r="D90" s="5" t="n">
-        <v>-0.21</v>
+        <v>-0.209</v>
       </c>
       <c r="E90" s="5" t="n">
         <v>-0.107</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>-0.174</v>
+        <v>-0.173</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>-0.107</v>
+        <v>-0.106</v>
       </c>
       <c r="H90" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>-1.321</v>
+        <v>-1.316</v>
       </c>
     </row>
     <row r="91">
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="D91" s="5" t="n">
-        <v>-0.268</v>
+        <v>-0.267</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>-0.145</v>
+        <v>-0.144</v>
       </c>
       <c r="F91" s="5" t="n">
         <v>-0.197</v>
@@ -3393,7 +3393,7 @@
         <v>-0</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>-1.69</v>
+        <v>-1.682</v>
       </c>
     </row>
     <row r="92">
@@ -3873,22 +3873,22 @@
         </is>
       </c>
       <c r="D106" s="5" t="n">
-        <v>-0.002</v>
+        <v>-0.003</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>-0.458</v>
+        <v>-0.455</v>
       </c>
       <c r="F106" s="5" t="n">
         <v>-0.222</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>-0.222</v>
+        <v>-0.223</v>
       </c>
       <c r="H106" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>-0.006</v>
+        <v>-0.011</v>
       </c>
     </row>
     <row r="107">
@@ -3915,7 +3915,7 @@
         <v>-0.342</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>-0.268</v>
+        <v>-0.269</v>
       </c>
       <c r="H107" s="5" t="n">
         <v>-0</v>
@@ -3939,22 +3939,22 @@
         </is>
       </c>
       <c r="D108" s="5" t="n">
-        <v>-0</v>
+        <v>-0.001</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>-0.439</v>
+        <v>-0.438</v>
       </c>
       <c r="F108" s="5" t="n">
         <v>-0.382</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>-0.284</v>
+        <v>-0.285</v>
       </c>
       <c r="H108" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I108" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.005</v>
       </c>
     </row>
     <row r="109">
@@ -3972,22 +3972,22 @@
         </is>
       </c>
       <c r="D109" s="5" t="n">
-        <v>-0.002</v>
+        <v>-0.004</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>-0.46</v>
+        <v>-0.454</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>-0.223</v>
+        <v>-0.22</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>-0.223</v>
+        <v>-0.221</v>
       </c>
       <c r="H109" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>-0.006</v>
+        <v>-0.011</v>
       </c>
     </row>
     <row r="110">
@@ -4011,10 +4011,10 @@
         <v>-0.023</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>-0.344</v>
+        <v>-0.339</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>-0.269</v>
+        <v>-0.266</v>
       </c>
       <c r="H110" s="5" t="n">
         <v>-0</v>
@@ -4041,19 +4041,19 @@
         <v>-0.001</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>-0.442</v>
+        <v>-0.434</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>-0.384</v>
+        <v>-0.378</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>-0.284</v>
+        <v>-0.281</v>
       </c>
       <c r="H111" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.005</v>
       </c>
     </row>
     <row r="112">
@@ -7267,13 +7267,13 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.5</v>
+        <v>0.499</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2.023</v>
+        <v>2.018</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>0.136</v>
@@ -7282,7 +7282,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>1.915</v>
+        <v>1.909</v>
       </c>
     </row>
     <row r="7">
@@ -7303,19 +7303,19 @@
         <v>0.254</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2.047</v>
+        <v>2.046</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.277</v>
+        <v>0.276</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.177</v>
+        <v>0.176</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>1.174</v>
+        <v>1.168</v>
       </c>
     </row>
     <row r="8">
@@ -7333,22 +7333,22 @@
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.3</v>
+        <v>0.299</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1.296</v>
+        <v>1.294</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.313</v>
+        <v>0.312</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.191</v>
+        <v>0.19</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>1.588</v>
+        <v>1.581</v>
       </c>
     </row>
     <row r="9">
@@ -7366,22 +7366,22 @@
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.646</v>
+        <v>0.644</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>2.076</v>
+        <v>2.071</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.136</v>
+        <v>0.135</v>
       </c>
       <c r="H9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>1.946</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="10">
@@ -7399,22 +7399,22 @@
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.165</v>
+        <v>0.164</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>2.047</v>
+        <v>2.046</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.277</v>
+        <v>0.275</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.176</v>
+        <v>0.175</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>1.469</v>
+        <v>1.464</v>
       </c>
     </row>
     <row r="11">
@@ -7432,22 +7432,22 @@
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.236</v>
+        <v>0.235</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1.297</v>
+        <v>1.294</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.314</v>
+        <v>0.311</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.191</v>
+        <v>0.189</v>
       </c>
       <c r="H11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>1.793</v>
+        <v>1.786</v>
       </c>
     </row>
     <row r="12">
@@ -7477,7 +7477,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12" s="5" t="n">
         <v>0</v>
@@ -7927,22 +7927,22 @@
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>0.499</v>
+        <v>0.497</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>1.748</v>
+        <v>1.745</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.038</v>
+        <v>0.036</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>1.912</v>
+        <v>1.903</v>
       </c>
     </row>
     <row r="27">
@@ -7960,22 +7960,22 @@
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>0.254</v>
+        <v>0.253</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>2.033</v>
+        <v>2.032</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.016</v>
+        <v>0.014</v>
       </c>
       <c r="H27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>1.173</v>
+        <v>1.168</v>
       </c>
     </row>
     <row r="28">
@@ -7993,22 +7993,22 @@
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>0.3</v>
+        <v>0.299</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1.033</v>
+        <v>1.031</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.082</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="H28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>1.586</v>
+        <v>1.578</v>
       </c>
     </row>
     <row r="29">
@@ -8026,22 +8026,22 @@
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>0.645</v>
+        <v>0.642</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>1.801</v>
+        <v>1.799</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.037</v>
+        <v>0.038</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H29" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>1.942</v>
+        <v>1.933</v>
       </c>
     </row>
     <row r="30">
@@ -8059,22 +8059,22 @@
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>0.165</v>
+        <v>0.164</v>
       </c>
       <c r="E30" s="5" t="n">
         <v>2.033</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.015</v>
+        <v>0.016</v>
       </c>
       <c r="H30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>1.469</v>
+        <v>1.463</v>
       </c>
     </row>
     <row r="31">
@@ -8092,22 +8092,22 @@
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>0.235</v>
+        <v>0.234</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1.031</v>
+        <v>1.033</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.083</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="H31" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>1.791</v>
+        <v>1.783</v>
       </c>
     </row>
     <row r="32">
@@ -8170,7 +8170,7 @@
         <v>-0</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I33" s="5" t="n">
         <v>0</v>
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>0.172</v>
+        <v>0.171</v>
       </c>
       <c r="E35" s="5" t="n">
         <v>0.648</v>
@@ -8236,7 +8236,7 @@
         <v>-0</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I35" s="5" t="n">
         <v>0</v>
@@ -8266,7 +8266,7 @@
         <v>-0</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H36" s="5" t="n">
         <v>0</v>
@@ -8332,7 +8332,7 @@
         <v>-0</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H38" s="5" t="n">
         <v>-0</v>
@@ -8425,13 +8425,13 @@
         <v>0</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0.263</v>
+        <v>0.264</v>
       </c>
       <c r="F41" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H41" s="5" t="n">
         <v>-0</v>
@@ -8464,7 +8464,7 @@
         <v>-0</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H42" s="5" t="n">
         <v>-0</v>
@@ -8497,7 +8497,7 @@
         <v>-0</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H43" s="5" t="n">
         <v>-0</v>
@@ -8587,22 +8587,22 @@
         </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>-0.501</v>
+        <v>-0.499</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0.497</v>
+        <v>0.501</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>-0.041</v>
+        <v>-0.039</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.026</v>
+        <v>-0.025</v>
       </c>
       <c r="H46" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>-1.907</v>
+        <v>-1.898</v>
       </c>
     </row>
     <row r="47">
@@ -8620,22 +8620,22 @@
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>-0.165</v>
+        <v>-0.164</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>1.832</v>
+        <v>1.833</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.037</v>
+        <v>-0.036</v>
       </c>
       <c r="H47" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>-1.469</v>
+        <v>-1.463</v>
       </c>
     </row>
     <row r="48">
@@ -8653,22 +8653,22 @@
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>-0.235</v>
+        <v>-0.234</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>1.006</v>
+        <v>1.008</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>-0.082</v>
+        <v>-0.08</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.041</v>
+        <v>-0.04</v>
       </c>
       <c r="H48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>-1.791</v>
+        <v>-1.783</v>
       </c>
     </row>
     <row r="49">
@@ -8686,22 +8686,22 @@
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>-0.642</v>
+        <v>-0.639</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0.549</v>
+        <v>0.551</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>-0.04</v>
+        <v>-0.041</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.025</v>
+        <v>-0.026</v>
       </c>
       <c r="H49" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>-1.947</v>
+        <v>-1.937</v>
       </c>
     </row>
     <row r="50">
@@ -8719,13 +8719,13 @@
         </is>
       </c>
       <c r="D50" s="5" t="n">
-        <v>-0.254</v>
+        <v>-0.253</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>1.832</v>
+        <v>1.833</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="G50" s="5" t="n">
         <v>-0.037</v>
@@ -8734,7 +8734,7 @@
         <v>-0</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>-1.173</v>
+        <v>-1.168</v>
       </c>
     </row>
     <row r="51">
@@ -8752,22 +8752,22 @@
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>-0.3</v>
+        <v>-0.299</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>1.007</v>
+        <v>1.005</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>-0.081</v>
+        <v>-0.082</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.041</v>
+        <v>-0.042</v>
       </c>
       <c r="H51" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>-1.586</v>
+        <v>-1.578</v>
       </c>
     </row>
     <row r="52">
@@ -8830,7 +8830,7 @@
         <v>0</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I53" s="5" t="n">
         <v>-0</v>
@@ -8896,7 +8896,7 @@
         <v>0</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I55" s="5" t="n">
         <v>-0</v>
@@ -8926,7 +8926,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H56" s="5" t="n">
         <v>0</v>
@@ -8992,7 +8992,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H58" s="5" t="n">
         <v>-0</v>
@@ -9091,7 +9091,7 @@
         <v>0</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H61" s="5" t="n">
         <v>-0</v>
@@ -9157,7 +9157,7 @@
         <v>0</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H63" s="5" t="n">
         <v>-0</v>
@@ -9247,13 +9247,13 @@
         </is>
       </c>
       <c r="D66" s="5" t="n">
-        <v>-0.502</v>
+        <v>-0.501</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0.223</v>
+        <v>0.228</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>-0.174</v>
+        <v>-0.173</v>
       </c>
       <c r="G66" s="5" t="n">
         <v>-0.159</v>
@@ -9262,7 +9262,7 @@
         <v>-0</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>-1.911</v>
+        <v>-1.905</v>
       </c>
     </row>
     <row r="67">
@@ -9280,22 +9280,22 @@
         </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>-0.165</v>
+        <v>-0.164</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>1.818</v>
+        <v>1.819</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>-0.276</v>
+        <v>-0.275</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>-0.198</v>
+        <v>-0.197</v>
       </c>
       <c r="H67" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>-1.469</v>
+        <v>-1.464</v>
       </c>
     </row>
     <row r="68">
@@ -9313,22 +9313,22 @@
         </is>
       </c>
       <c r="D68" s="5" t="n">
-        <v>-0.236</v>
+        <v>-0.235</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>0.743</v>
+        <v>0.745</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>-0.311</v>
+        <v>-0.309</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>-0.212</v>
+        <v>-0.211</v>
       </c>
       <c r="H68" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>-1.793</v>
+        <v>-1.786</v>
       </c>
     </row>
     <row r="69">
@@ -9346,22 +9346,22 @@
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>-0.643</v>
+        <v>-0.641</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>0.273</v>
+        <v>0.278</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>-0.174</v>
+        <v>-0.173</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>-0.159</v>
+        <v>-0.158</v>
       </c>
       <c r="H69" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>-1.95</v>
+        <v>-1.944</v>
       </c>
     </row>
     <row r="70">
@@ -9385,16 +9385,16 @@
         <v>1.819</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>-0.277</v>
+        <v>-0.275</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>-0.198</v>
+        <v>-0.197</v>
       </c>
       <c r="H70" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>-1.174</v>
+        <v>-1.168</v>
       </c>
     </row>
     <row r="71">
@@ -9412,22 +9412,22 @@
         </is>
       </c>
       <c r="D71" s="5" t="n">
-        <v>-0.3</v>
+        <v>-0.299</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>0.742</v>
+        <v>0.745</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>-0.311</v>
+        <v>-0.309</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>-0.212</v>
+        <v>-0.21</v>
       </c>
       <c r="H71" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>-1.588</v>
+        <v>-1.581</v>
       </c>
     </row>
     <row r="72">
@@ -9523,7 +9523,7 @@
         <v>-0</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I74" s="5" t="n">
         <v>-0</v>
@@ -9544,7 +9544,7 @@
         </is>
       </c>
       <c r="D75" s="5" t="n">
-        <v>-0.173</v>
+        <v>-0.172</v>
       </c>
       <c r="E75" s="5" t="n">
         <v>0.636</v>
@@ -9907,22 +9907,22 @@
         </is>
       </c>
       <c r="D86" s="5" t="n">
-        <v>0.151</v>
+        <v>0.152</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>1.81</v>
+        <v>1.805</v>
       </c>
       <c r="F86" s="5" t="n">
         <v>0.252</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.235</v>
+        <v>0.236</v>
       </c>
       <c r="H86" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>0.581</v>
+        <v>0.584</v>
       </c>
     </row>
     <row r="87">
@@ -9940,7 +9940,7 @@
         </is>
       </c>
       <c r="D87" s="5" t="n">
-        <v>0.108</v>
+        <v>0.107</v>
       </c>
       <c r="E87" s="5" t="n">
         <v>1.988</v>
@@ -9955,7 +9955,7 @@
         <v>0</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>0.249</v>
+        <v>0.248</v>
       </c>
     </row>
     <row r="88">
@@ -9976,13 +9976,13 @@
         <v>0.113</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>1.503</v>
+        <v>1.5</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.308</v>
+        <v>0.309</v>
       </c>
       <c r="H88" s="5" t="n">
         <v>0</v>
@@ -10006,22 +10006,22 @@
         </is>
       </c>
       <c r="D89" s="5" t="n">
-        <v>0.196</v>
+        <v>0.197</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>1.863</v>
+        <v>1.857</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>0.253</v>
+        <v>0.25</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.235</v>
+        <v>0.233</v>
       </c>
       <c r="H89" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>0.588</v>
+        <v>0.591</v>
       </c>
     </row>
     <row r="90">
@@ -10039,22 +10039,22 @@
         </is>
       </c>
       <c r="D90" s="5" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="E90" s="5" t="n">
         <v>1.988</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.397</v>
+        <v>0.391</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.29</v>
+        <v>0.287</v>
       </c>
       <c r="H90" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>0.545</v>
+        <v>0.544</v>
       </c>
     </row>
     <row r="91">
@@ -10072,16 +10072,16 @@
         </is>
       </c>
       <c r="D91" s="5" t="n">
-        <v>0.049</v>
+        <v>0.048</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>1.505</v>
+        <v>1.497</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>0.444</v>
+        <v>0.438</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.309</v>
+        <v>0.305</v>
       </c>
       <c r="H91" s="5" t="n">
         <v>0</v>
@@ -10117,7 +10117,7 @@
         <v>0</v>
       </c>
       <c r="H92" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I92" s="5" t="n">
         <v>0</v>
@@ -10567,22 +10567,22 @@
         </is>
       </c>
       <c r="D106" s="5" t="n">
-        <v>0.148</v>
+        <v>0.146</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0.894</v>
+        <v>0.896</v>
       </c>
       <c r="F106" s="5" t="n">
         <v>-0.192</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>-0.21</v>
+        <v>-0.211</v>
       </c>
       <c r="H106" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>0.57</v>
+        <v>0.5620000000000001</v>
       </c>
     </row>
     <row r="107">
@@ -10603,19 +10603,19 @@
         <v>0.107</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>1.942</v>
+        <v>1.941</v>
       </c>
       <c r="F107" s="5" t="n">
         <v>-0.29</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>-0.247</v>
+        <v>-0.248</v>
       </c>
       <c r="H107" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>0.248</v>
+        <v>0.246</v>
       </c>
     </row>
     <row r="108">
@@ -10633,7 +10633,7 @@
         </is>
       </c>
       <c r="D108" s="5" t="n">
-        <v>0.112</v>
+        <v>0.111</v>
       </c>
       <c r="E108" s="5" t="n">
         <v>0.624</v>
@@ -10642,13 +10642,13 @@
         <v>-0.322</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>-0.259</v>
+        <v>-0.261</v>
       </c>
       <c r="H108" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I108" s="5" t="n">
-        <v>0.402</v>
+        <v>0.397</v>
       </c>
     </row>
     <row r="109">
@@ -10666,22 +10666,22 @@
         </is>
       </c>
       <c r="D109" s="5" t="n">
-        <v>0.192</v>
+        <v>0.19</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0.944</v>
+        <v>0.949</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>-0.193</v>
+        <v>-0.19</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>-0.21</v>
+        <v>-0.208</v>
       </c>
       <c r="H109" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>0.576</v>
+        <v>0.5679999999999999</v>
       </c>
     </row>
     <row r="110">
@@ -10705,16 +10705,16 @@
         <v>1.942</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>-0.291</v>
+        <v>-0.287</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>-0.248</v>
+        <v>-0.245</v>
       </c>
       <c r="H110" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>0.543</v>
+        <v>0.541</v>
       </c>
     </row>
     <row r="111">
@@ -10735,19 +10735,19 @@
         <v>0.047</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>0.621</v>
+        <v>0.628</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>-0.324</v>
+        <v>-0.318</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>-0.26</v>
+        <v>-0.257</v>
       </c>
       <c r="H111" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>0.607</v>
+        <v>0.602</v>
       </c>
     </row>
     <row r="112">
@@ -10837,13 +10837,13 @@
         <v>0.601</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>-0.007</v>
+        <v>-0.008</v>
       </c>
       <c r="G114" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="H114" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I114" s="5" t="n">
         <v>0</v>
@@ -10864,7 +10864,7 @@
         </is>
       </c>
       <c r="D115" s="5" t="n">
-        <v>0.051</v>
+        <v>0.05</v>
       </c>
       <c r="E115" s="5" t="n">
         <v>0.643</v>
@@ -11227,22 +11227,22 @@
         </is>
       </c>
       <c r="D126" s="5" t="n">
-        <v>-0.15</v>
+        <v>-0.148</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>1.352</v>
+        <v>1.35</v>
       </c>
       <c r="F126" s="5" t="n">
         <v>0.189</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.187</v>
+        <v>0.188</v>
       </c>
       <c r="H126" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I126" s="5" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.5580000000000001</v>
       </c>
     </row>
     <row r="127">
@@ -11263,19 +11263,19 @@
         <v>-0.018</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>1.923</v>
+        <v>1.924</v>
       </c>
       <c r="F127" s="5" t="n">
         <v>0.291</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.225</v>
+        <v>0.227</v>
       </c>
       <c r="H127" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I127" s="5" t="n">
-        <v>-0.543</v>
+        <v>-0.542</v>
       </c>
     </row>
     <row r="128">
@@ -11293,7 +11293,7 @@
         </is>
       </c>
       <c r="D128" s="5" t="n">
-        <v>-0.048</v>
+        <v>-0.047</v>
       </c>
       <c r="E128" s="5" t="n">
         <v>1.415</v>
@@ -11302,13 +11302,13 @@
         <v>0.324</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.238</v>
+        <v>0.24</v>
       </c>
       <c r="H128" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I128" s="5" t="n">
-        <v>-0.607</v>
+        <v>-0.602</v>
       </c>
     </row>
     <row r="129">
@@ -11326,22 +11326,22 @@
         </is>
       </c>
       <c r="D129" s="5" t="n">
-        <v>-0.19</v>
+        <v>-0.188</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>1.405</v>
+        <v>1.401</v>
       </c>
       <c r="F129" s="5" t="n">
-        <v>0.19</v>
+        <v>0.187</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.187</v>
+        <v>0.185</v>
       </c>
       <c r="H129" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I129" s="5" t="n">
-        <v>-0.58</v>
+        <v>-0.573</v>
       </c>
     </row>
     <row r="130">
@@ -11365,16 +11365,16 @@
         <v>1.924</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>0.292</v>
+        <v>0.287</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.226</v>
+        <v>0.223</v>
       </c>
       <c r="H130" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I130" s="5" t="n">
-        <v>-0.248</v>
+        <v>-0.246</v>
       </c>
     </row>
     <row r="131">
@@ -11392,22 +11392,22 @@
         </is>
       </c>
       <c r="D131" s="5" t="n">
-        <v>-0.112</v>
+        <v>-0.111</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>1.418</v>
+        <v>1.41</v>
       </c>
       <c r="F131" s="5" t="n">
-        <v>0.326</v>
+        <v>0.32</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.239</v>
+        <v>0.236</v>
       </c>
       <c r="H131" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I131" s="5" t="n">
-        <v>-0.402</v>
+        <v>-0.397</v>
       </c>
     </row>
     <row r="132">
@@ -11437,7 +11437,7 @@
         <v>0</v>
       </c>
       <c r="H132" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I132" s="5" t="n">
         <v>-0</v>
@@ -11497,7 +11497,7 @@
         <v>0.6</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="G134" s="5" t="n">
         <v>0</v>
@@ -11887,22 +11887,22 @@
         </is>
       </c>
       <c r="D146" s="5" t="n">
-        <v>-0.153</v>
+        <v>-0.154</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>0.436</v>
+        <v>0.441</v>
       </c>
       <c r="F146" s="5" t="n">
         <v>-0.255</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>-0.258</v>
+        <v>-0.259</v>
       </c>
       <c r="H146" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I146" s="5" t="n">
-        <v>-0.577</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="147">
@@ -11920,7 +11920,7 @@
         </is>
       </c>
       <c r="D147" s="5" t="n">
-        <v>-0.019</v>
+        <v>-0.018</v>
       </c>
       <c r="E147" s="5" t="n">
         <v>1.877</v>
@@ -11929,13 +11929,13 @@
         <v>-0.394</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>-0.311</v>
+        <v>-0.312</v>
       </c>
       <c r="H147" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I147" s="5" t="n">
-        <v>-0.545</v>
+        <v>-0.543</v>
       </c>
     </row>
     <row r="148">
@@ -11953,16 +11953,16 @@
         </is>
       </c>
       <c r="D148" s="5" t="n">
-        <v>-0.048</v>
+        <v>-0.049</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>0.536</v>
+        <v>0.539</v>
       </c>
       <c r="F148" s="5" t="n">
         <v>-0.44</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>-0.329</v>
+        <v>-0.33</v>
       </c>
       <c r="H148" s="5" t="n">
         <v>-0</v>
@@ -11986,22 +11986,22 @@
         </is>
       </c>
       <c r="D149" s="5" t="n">
-        <v>-0.194</v>
+        <v>-0.195</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>0.486</v>
+        <v>0.492</v>
       </c>
       <c r="F149" s="5" t="n">
+        <v>-0.253</v>
+      </c>
+      <c r="G149" s="5" t="n">
         <v>-0.256</v>
       </c>
-      <c r="G149" s="5" t="n">
-        <v>-0.258</v>
-      </c>
       <c r="H149" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I149" s="5" t="n">
-        <v>-0.592</v>
+        <v>-0.595</v>
       </c>
     </row>
     <row r="150">
@@ -12025,16 +12025,16 @@
         <v>1.878</v>
       </c>
       <c r="F150" s="5" t="n">
-        <v>-0.396</v>
+        <v>-0.39</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>-0.312</v>
+        <v>-0.309</v>
       </c>
       <c r="H150" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I150" s="5" t="n">
-        <v>-0.249</v>
+        <v>-0.248</v>
       </c>
     </row>
     <row r="151">
@@ -12055,13 +12055,13 @@
         <v>-0.113</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>0.534</v>
+        <v>0.542</v>
       </c>
       <c r="F151" s="5" t="n">
-        <v>-0.442</v>
+        <v>-0.436</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>-0.33</v>
+        <v>-0.326</v>
       </c>
       <c r="H151" s="5" t="n">
         <v>-0</v>
@@ -12163,7 +12163,7 @@
         <v>-0</v>
       </c>
       <c r="H154" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I154" s="5" t="n">
         <v>-0</v>
@@ -12184,7 +12184,7 @@
         </is>
       </c>
       <c r="D155" s="5" t="n">
-        <v>-0.052</v>
+        <v>-0.053</v>
       </c>
       <c r="E155" s="5" t="n">
         <v>0.64</v>
@@ -16507,22 +16507,22 @@
         </is>
       </c>
       <c r="D286" s="5" t="n">
-        <v>0.702</v>
+        <v>0.7</v>
       </c>
       <c r="E286" s="5" t="n">
-        <v>2.441</v>
+        <v>2.434</v>
       </c>
       <c r="F286" s="5" t="n">
-        <v>0.24</v>
+        <v>0.239</v>
       </c>
       <c r="G286" s="5" t="n">
-        <v>0.195</v>
+        <v>0.194</v>
       </c>
       <c r="H286" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I286" s="5" t="n">
-        <v>2.685</v>
+        <v>2.677</v>
       </c>
     </row>
     <row r="287">
@@ -16540,22 +16540,22 @@
         </is>
       </c>
       <c r="D287" s="5" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="E287" s="5" t="n">
         <v>2.189</v>
       </c>
       <c r="F287" s="5" t="n">
-        <v>0.389</v>
+        <v>0.386</v>
       </c>
       <c r="G287" s="5" t="n">
-        <v>0.251</v>
+        <v>0.25</v>
       </c>
       <c r="H287" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I287" s="5" t="n">
-        <v>1.698</v>
+        <v>1.691</v>
       </c>
     </row>
     <row r="288">
@@ -16573,22 +16573,22 @@
         </is>
       </c>
       <c r="D288" s="5" t="n">
-        <v>0.41</v>
+        <v>0.408</v>
       </c>
       <c r="E288" s="5" t="n">
-        <v>1.459</v>
+        <v>1.455</v>
       </c>
       <c r="F288" s="5" t="n">
-        <v>0.439</v>
+        <v>0.437</v>
       </c>
       <c r="G288" s="5" t="n">
-        <v>0.271</v>
+        <v>0.27</v>
       </c>
       <c r="H288" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I288" s="5" t="n">
-        <v>2.263</v>
+        <v>2.254</v>
       </c>
     </row>
     <row r="289">
@@ -16606,22 +16606,22 @@
         </is>
       </c>
       <c r="D289" s="5" t="n">
-        <v>0.905</v>
+        <v>0.903</v>
       </c>
       <c r="E289" s="5" t="n">
-        <v>2.498</v>
+        <v>2.491</v>
       </c>
       <c r="F289" s="5" t="n">
-        <v>0.24</v>
+        <v>0.238</v>
       </c>
       <c r="G289" s="5" t="n">
-        <v>0.195</v>
+        <v>0.194</v>
       </c>
       <c r="H289" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I289" s="5" t="n">
-        <v>2.73</v>
+        <v>2.721</v>
       </c>
     </row>
     <row r="290">
@@ -16639,22 +16639,22 @@
         </is>
       </c>
       <c r="D290" s="5" t="n">
-        <v>0.247</v>
+        <v>0.246</v>
       </c>
       <c r="E290" s="5" t="n">
         <v>2.189</v>
       </c>
       <c r="F290" s="5" t="n">
-        <v>0.389</v>
+        <v>0.386</v>
       </c>
       <c r="G290" s="5" t="n">
-        <v>0.251</v>
+        <v>0.25</v>
       </c>
       <c r="H290" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I290" s="5" t="n">
-        <v>2.008</v>
+        <v>2.001</v>
       </c>
     </row>
     <row r="291">
@@ -16672,22 +16672,22 @@
         </is>
       </c>
       <c r="D291" s="5" t="n">
-        <v>0.342</v>
+        <v>0.34</v>
       </c>
       <c r="E291" s="5" t="n">
-        <v>1.459</v>
+        <v>1.456</v>
       </c>
       <c r="F291" s="5" t="n">
-        <v>0.44</v>
+        <v>0.436</v>
       </c>
       <c r="G291" s="5" t="n">
-        <v>0.271</v>
+        <v>0.269</v>
       </c>
       <c r="H291" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I291" s="5" t="n">
-        <v>2.479</v>
+        <v>2.469</v>
       </c>
     </row>
     <row r="292">
@@ -16717,7 +16717,7 @@
         <v>0</v>
       </c>
       <c r="H292" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I292" s="5" t="n">
         <v>0</v>
@@ -16804,7 +16804,7 @@
         </is>
       </c>
       <c r="D295" s="5" t="n">
-        <v>0.242</v>
+        <v>0.241</v>
       </c>
       <c r="E295" s="5" t="n">
         <v>0.6830000000000001</v>
@@ -17167,22 +17167,22 @@
         </is>
       </c>
       <c r="D306" s="5" t="n">
-        <v>0.701</v>
+        <v>0.697</v>
       </c>
       <c r="E306" s="5" t="n">
-        <v>2.056</v>
+        <v>2.052</v>
       </c>
       <c r="F306" s="5" t="n">
-        <v>0.053</v>
+        <v>0.052</v>
       </c>
       <c r="G306" s="5" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="H306" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I306" s="5" t="n">
-        <v>2.68</v>
+        <v>2.668</v>
       </c>
     </row>
     <row r="307">
@@ -17200,22 +17200,22 @@
         </is>
       </c>
       <c r="D307" s="5" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="E307" s="5" t="n">
-        <v>2.17</v>
+        <v>2.169</v>
       </c>
       <c r="F307" s="5" t="n">
-        <v>0.1</v>
+        <v>0.098</v>
       </c>
       <c r="G307" s="5" t="n">
-        <v>0.026</v>
+        <v>0.024</v>
       </c>
       <c r="H307" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I307" s="5" t="n">
-        <v>1.697</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="308">
@@ -17233,22 +17233,22 @@
         </is>
       </c>
       <c r="D308" s="5" t="n">
-        <v>0.409</v>
+        <v>0.407</v>
       </c>
       <c r="E308" s="5" t="n">
-        <v>1.089</v>
+        <v>1.086</v>
       </c>
       <c r="F308" s="5" t="n">
-        <v>0.118</v>
+        <v>0.115</v>
       </c>
       <c r="G308" s="5" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
       <c r="H308" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I308" s="5" t="n">
-        <v>2.261</v>
+        <v>2.249</v>
       </c>
     </row>
     <row r="309">
@@ -17266,22 +17266,22 @@
         </is>
       </c>
       <c r="D309" s="5" t="n">
-        <v>0.904</v>
+        <v>0.899</v>
       </c>
       <c r="E309" s="5" t="n">
-        <v>2.111</v>
+        <v>2.109</v>
       </c>
       <c r="F309" s="5" t="n">
         <v>0.053</v>
       </c>
       <c r="G309" s="5" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="H309" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I309" s="5" t="n">
-        <v>2.725</v>
+        <v>2.712</v>
       </c>
     </row>
     <row r="310">
@@ -17299,22 +17299,22 @@
         </is>
       </c>
       <c r="D310" s="5" t="n">
-        <v>0.247</v>
+        <v>0.246</v>
       </c>
       <c r="E310" s="5" t="n">
-        <v>2.17</v>
+        <v>2.169</v>
       </c>
       <c r="F310" s="5" t="n">
-        <v>0.099</v>
+        <v>0.101</v>
       </c>
       <c r="G310" s="5" t="n">
-        <v>0.025</v>
+        <v>0.026</v>
       </c>
       <c r="H310" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I310" s="5" t="n">
-        <v>2.008</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311">
@@ -17332,22 +17332,22 @@
         </is>
       </c>
       <c r="D311" s="5" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="E311" s="5" t="n">
-        <v>1.087</v>
+        <v>1.09</v>
       </c>
       <c r="F311" s="5" t="n">
-        <v>0.117</v>
+        <v>0.118</v>
       </c>
       <c r="G311" s="5" t="n">
-        <v>0.032</v>
+        <v>0.033</v>
       </c>
       <c r="H311" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I311" s="5" t="n">
-        <v>2.476</v>
+        <v>2.465</v>
       </c>
     </row>
     <row r="312">
@@ -17377,7 +17377,7 @@
         <v>0</v>
       </c>
       <c r="H312" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I312" s="5" t="n">
         <v>0</v>
@@ -17410,7 +17410,7 @@
         <v>-0</v>
       </c>
       <c r="H313" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I313" s="5" t="n">
         <v>0</v>
@@ -17464,7 +17464,7 @@
         </is>
       </c>
       <c r="D315" s="5" t="n">
-        <v>0.241</v>
+        <v>0.24</v>
       </c>
       <c r="E315" s="5" t="n">
         <v>0.6820000000000001</v>
@@ -17476,7 +17476,7 @@
         <v>-0</v>
       </c>
       <c r="H315" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I315" s="5" t="n">
         <v>0</v>
@@ -17506,7 +17506,7 @@
         <v>-0</v>
       </c>
       <c r="G316" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H316" s="5" t="n">
         <v>0</v>
@@ -17572,7 +17572,7 @@
         <v>-0</v>
       </c>
       <c r="G318" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H318" s="5" t="n">
         <v>-0</v>
@@ -17671,7 +17671,7 @@
         <v>-0</v>
       </c>
       <c r="G321" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H321" s="5" t="n">
         <v>-0</v>
@@ -17737,7 +17737,7 @@
         <v>-0</v>
       </c>
       <c r="G323" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H323" s="5" t="n">
         <v>-0</v>
@@ -17827,22 +17827,22 @@
         </is>
       </c>
       <c r="D326" s="5" t="n">
-        <v>-0.703</v>
+        <v>-0.7</v>
       </c>
       <c r="E326" s="5" t="n">
-        <v>0.302</v>
+        <v>0.306</v>
       </c>
       <c r="F326" s="5" t="n">
-        <v>-0.056</v>
+        <v>-0.055</v>
       </c>
       <c r="G326" s="5" t="n">
-        <v>-0.032</v>
+        <v>-0.031</v>
       </c>
       <c r="H326" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I326" s="5" t="n">
-        <v>-2.676</v>
+        <v>-2.663</v>
       </c>
     </row>
     <row r="327">
@@ -17860,22 +17860,22 @@
         </is>
       </c>
       <c r="D327" s="5" t="n">
-        <v>-0.247</v>
+        <v>-0.246</v>
       </c>
       <c r="E327" s="5" t="n">
-        <v>1.888</v>
+        <v>1.889</v>
       </c>
       <c r="F327" s="5" t="n">
-        <v>-0.1</v>
+        <v>-0.097</v>
       </c>
       <c r="G327" s="5" t="n">
-        <v>-0.048</v>
+        <v>-0.047</v>
       </c>
       <c r="H327" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I327" s="5" t="n">
-        <v>-2.008</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="328">
@@ -17893,22 +17893,22 @@
         </is>
       </c>
       <c r="D328" s="5" t="n">
-        <v>-0.341</v>
+        <v>-0.34</v>
       </c>
       <c r="E328" s="5" t="n">
-        <v>1.052</v>
+        <v>1.055</v>
       </c>
       <c r="F328" s="5" t="n">
-        <v>-0.115</v>
+        <v>-0.113</v>
       </c>
       <c r="G328" s="5" t="n">
-        <v>-0.054</v>
+        <v>-0.053</v>
       </c>
       <c r="H328" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I328" s="5" t="n">
-        <v>-2.476</v>
+        <v>-2.464</v>
       </c>
     </row>
     <row r="329">
@@ -17926,22 +17926,22 @@
         </is>
       </c>
       <c r="D329" s="5" t="n">
-        <v>-0.901</v>
+        <v>-0.897</v>
       </c>
       <c r="E329" s="5" t="n">
-        <v>0.356</v>
+        <v>0.358</v>
       </c>
       <c r="F329" s="5" t="n">
-        <v>-0.056</v>
+        <v>-0.057</v>
       </c>
       <c r="G329" s="5" t="n">
-        <v>-0.031</v>
+        <v>-0.032</v>
       </c>
       <c r="H329" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I329" s="5" t="n">
-        <v>-2.729</v>
+        <v>-2.717</v>
       </c>
     </row>
     <row r="330">
@@ -17959,22 +17959,22 @@
         </is>
       </c>
       <c r="D330" s="5" t="n">
-        <v>-0.341</v>
+        <v>-0.34</v>
       </c>
       <c r="E330" s="5" t="n">
         <v>1.889</v>
       </c>
       <c r="F330" s="5" t="n">
-        <v>-0.099</v>
+        <v>-0.1</v>
       </c>
       <c r="G330" s="5" t="n">
-        <v>-0.048</v>
+        <v>-0.049</v>
       </c>
       <c r="H330" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I330" s="5" t="n">
-        <v>-1.697</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="331">
@@ -17992,22 +17992,22 @@
         </is>
       </c>
       <c r="D331" s="5" t="n">
-        <v>-0.409</v>
+        <v>-0.407</v>
       </c>
       <c r="E331" s="5" t="n">
-        <v>1.053</v>
+        <v>1.05</v>
       </c>
       <c r="F331" s="5" t="n">
-        <v>-0.114</v>
+        <v>-0.116</v>
       </c>
       <c r="G331" s="5" t="n">
-        <v>-0.054</v>
+        <v>-0.055</v>
       </c>
       <c r="H331" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I331" s="5" t="n">
-        <v>-2.261</v>
+        <v>-2.249</v>
       </c>
     </row>
     <row r="332">
@@ -18070,7 +18070,7 @@
         <v>0</v>
       </c>
       <c r="H333" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I333" s="5" t="n">
         <v>-0</v>
@@ -18124,7 +18124,7 @@
         </is>
       </c>
       <c r="D335" s="5" t="n">
-        <v>-0.242</v>
+        <v>-0.241</v>
       </c>
       <c r="E335" s="5" t="n">
         <v>0.666</v>
@@ -18136,7 +18136,7 @@
         <v>0</v>
       </c>
       <c r="H335" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I335" s="5" t="n">
         <v>-0</v>
@@ -18166,7 +18166,7 @@
         <v>0</v>
       </c>
       <c r="G336" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H336" s="5" t="n">
         <v>0</v>
@@ -18232,7 +18232,7 @@
         <v>0</v>
       </c>
       <c r="G338" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H338" s="5" t="n">
         <v>-0</v>
@@ -18331,7 +18331,7 @@
         <v>0</v>
       </c>
       <c r="G341" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H341" s="5" t="n">
         <v>-0</v>
@@ -18397,7 +18397,7 @@
         <v>0</v>
       </c>
       <c r="G343" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H343" s="5" t="n">
         <v>-0</v>
@@ -18487,22 +18487,22 @@
         </is>
       </c>
       <c r="D346" s="5" t="n">
-        <v>-0.704</v>
+        <v>-0.702</v>
       </c>
       <c r="E346" s="5" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.076</v>
       </c>
       <c r="F346" s="5" t="n">
-        <v>-0.243</v>
+        <v>-0.242</v>
       </c>
       <c r="G346" s="5" t="n">
-        <v>-0.219</v>
+        <v>-0.218</v>
       </c>
       <c r="H346" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I346" s="5" t="n">
-        <v>-2.681</v>
+        <v>-2.672</v>
       </c>
     </row>
     <row r="347">
@@ -18520,22 +18520,22 @@
         </is>
       </c>
       <c r="D347" s="5" t="n">
-        <v>-0.247</v>
+        <v>-0.246</v>
       </c>
       <c r="E347" s="5" t="n">
-        <v>1.869</v>
+        <v>1.87</v>
       </c>
       <c r="F347" s="5" t="n">
-        <v>-0.388</v>
+        <v>-0.385</v>
       </c>
       <c r="G347" s="5" t="n">
-        <v>-0.274</v>
+        <v>-0.273</v>
       </c>
       <c r="H347" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I347" s="5" t="n">
-        <v>-2.008</v>
+        <v>-2.001</v>
       </c>
     </row>
     <row r="348">
@@ -18553,22 +18553,22 @@
         </is>
       </c>
       <c r="D348" s="5" t="n">
-        <v>-0.342</v>
+        <v>-0.34</v>
       </c>
       <c r="E348" s="5" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="F348" s="5" t="n">
-        <v>-0.437</v>
+        <v>-0.434</v>
       </c>
       <c r="G348" s="5" t="n">
-        <v>-0.293</v>
+        <v>-0.292</v>
       </c>
       <c r="H348" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I348" s="5" t="n">
-        <v>-2.478</v>
+        <v>-2.469</v>
       </c>
     </row>
     <row r="349">
@@ -18586,22 +18586,22 @@
         </is>
       </c>
       <c r="D349" s="5" t="n">
-        <v>-0.903</v>
+        <v>-0.9</v>
       </c>
       <c r="E349" s="5" t="n">
-        <v>-0.031</v>
+        <v>-0.024</v>
       </c>
       <c r="F349" s="5" t="n">
-        <v>-0.243</v>
+        <v>-0.242</v>
       </c>
       <c r="G349" s="5" t="n">
-        <v>-0.219</v>
+        <v>-0.218</v>
       </c>
       <c r="H349" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I349" s="5" t="n">
-        <v>-2.734</v>
+        <v>-2.726</v>
       </c>
     </row>
     <row r="350">
@@ -18619,22 +18619,22 @@
         </is>
       </c>
       <c r="D350" s="5" t="n">
-        <v>-0.341</v>
+        <v>-0.34</v>
       </c>
       <c r="E350" s="5" t="n">
-        <v>1.869</v>
+        <v>1.87</v>
       </c>
       <c r="F350" s="5" t="n">
-        <v>-0.388</v>
+        <v>-0.385</v>
       </c>
       <c r="G350" s="5" t="n">
-        <v>-0.274</v>
+        <v>-0.273</v>
       </c>
       <c r="H350" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I350" s="5" t="n">
-        <v>-1.698</v>
+        <v>-1.691</v>
       </c>
     </row>
     <row r="351">
@@ -18652,22 +18652,22 @@
         </is>
       </c>
       <c r="D351" s="5" t="n">
-        <v>-0.41</v>
+        <v>-0.408</v>
       </c>
       <c r="E351" s="5" t="n">
-        <v>0.681</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F351" s="5" t="n">
-        <v>-0.437</v>
+        <v>-0.434</v>
       </c>
       <c r="G351" s="5" t="n">
-        <v>-0.293</v>
+        <v>-0.291</v>
       </c>
       <c r="H351" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I351" s="5" t="n">
-        <v>-2.263</v>
+        <v>-2.254</v>
       </c>
     </row>
     <row r="352">
@@ -18763,7 +18763,7 @@
         <v>-0</v>
       </c>
       <c r="H354" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I354" s="5" t="n">
         <v>-0</v>
@@ -18784,7 +18784,7 @@
         </is>
       </c>
       <c r="D355" s="5" t="n">
-        <v>-0.242</v>
+        <v>-0.241</v>
       </c>
       <c r="E355" s="5" t="n">
         <v>0.666</v>
@@ -19147,22 +19147,22 @@
         </is>
       </c>
       <c r="D366" s="5" t="n">
-        <v>0.212</v>
+        <v>0.213</v>
       </c>
       <c r="E366" s="5" t="n">
-        <v>2.142</v>
+        <v>2.136</v>
       </c>
       <c r="F366" s="5" t="n">
         <v>0.354</v>
       </c>
       <c r="G366" s="5" t="n">
-        <v>0.334</v>
+        <v>0.335</v>
       </c>
       <c r="H366" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I366" s="5" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
     </row>
     <row r="367">
@@ -19183,19 +19183,19 @@
         <v>0.135</v>
       </c>
       <c r="E367" s="5" t="n">
-        <v>2.106</v>
+        <v>2.107</v>
       </c>
       <c r="F367" s="5" t="n">
-        <v>0.554</v>
+        <v>0.553</v>
       </c>
       <c r="G367" s="5" t="n">
-        <v>0.41</v>
+        <v>0.411</v>
       </c>
       <c r="H367" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I367" s="5" t="n">
-        <v>0.402</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="368">
@@ -19216,10 +19216,10 @@
         <v>0.147</v>
       </c>
       <c r="E368" s="5" t="n">
-        <v>1.748</v>
+        <v>1.745</v>
       </c>
       <c r="F368" s="5" t="n">
-        <v>0.62</v>
+        <v>0.619</v>
       </c>
       <c r="G368" s="5" t="n">
         <v>0.436</v>
@@ -19246,22 +19246,22 @@
         </is>
       </c>
       <c r="D369" s="5" t="n">
-        <v>0.275</v>
+        <v>0.276</v>
       </c>
       <c r="E369" s="5" t="n">
-        <v>2.199</v>
+        <v>2.191</v>
       </c>
       <c r="F369" s="5" t="n">
-        <v>0.355</v>
+        <v>0.351</v>
       </c>
       <c r="G369" s="5" t="n">
-        <v>0.334</v>
+        <v>0.331</v>
       </c>
       <c r="H369" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I369" s="5" t="n">
-        <v>0.825</v>
+        <v>0.829</v>
       </c>
     </row>
     <row r="370">
@@ -19279,22 +19279,22 @@
         </is>
       </c>
       <c r="D370" s="5" t="n">
-        <v>0.042</v>
+        <v>0.041</v>
       </c>
       <c r="E370" s="5" t="n">
-        <v>2.107</v>
+        <v>2.106</v>
       </c>
       <c r="F370" s="5" t="n">
-        <v>0.556</v>
+        <v>0.549</v>
       </c>
       <c r="G370" s="5" t="n">
-        <v>0.41</v>
+        <v>0.406</v>
       </c>
       <c r="H370" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I370" s="5" t="n">
-        <v>0.712</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="371">
@@ -19315,13 +19315,13 @@
         <v>0.079</v>
       </c>
       <c r="E371" s="5" t="n">
-        <v>1.751</v>
+        <v>1.74</v>
       </c>
       <c r="F371" s="5" t="n">
-        <v>0.623</v>
+        <v>0.614</v>
       </c>
       <c r="G371" s="5" t="n">
-        <v>0.436</v>
+        <v>0.432</v>
       </c>
       <c r="H371" s="5" t="n">
         <v>0</v>
@@ -19450,7 +19450,7 @@
         <v>0.678</v>
       </c>
       <c r="F375" s="5" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="G375" s="5" t="n">
         <v>0</v>
@@ -19807,22 +19807,22 @@
         </is>
       </c>
       <c r="D386" s="5" t="n">
-        <v>0.207</v>
+        <v>0.205</v>
       </c>
       <c r="E386" s="5" t="n">
-        <v>0.857</v>
+        <v>0.86</v>
       </c>
       <c r="F386" s="5" t="n">
-        <v>-0.268</v>
+        <v>-0.269</v>
       </c>
       <c r="G386" s="5" t="n">
-        <v>-0.29</v>
+        <v>-0.292</v>
       </c>
       <c r="H386" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I386" s="5" t="n">
-        <v>0.798</v>
+        <v>0.788</v>
       </c>
     </row>
     <row r="387">
@@ -19840,22 +19840,22 @@
         </is>
       </c>
       <c r="D387" s="5" t="n">
-        <v>0.135</v>
+        <v>0.134</v>
       </c>
       <c r="E387" s="5" t="n">
-        <v>2.042</v>
+        <v>2.041</v>
       </c>
       <c r="F387" s="5" t="n">
         <v>-0.407</v>
       </c>
       <c r="G387" s="5" t="n">
-        <v>-0.343</v>
+        <v>-0.344</v>
       </c>
       <c r="H387" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I387" s="5" t="n">
-        <v>0.4</v>
+        <v>0.397</v>
       </c>
     </row>
     <row r="388">
@@ -19873,22 +19873,22 @@
         </is>
       </c>
       <c r="D388" s="5" t="n">
-        <v>0.146</v>
+        <v>0.145</v>
       </c>
       <c r="E388" s="5" t="n">
-        <v>0.515</v>
+        <v>0.516</v>
       </c>
       <c r="F388" s="5" t="n">
         <v>-0.452</v>
       </c>
       <c r="G388" s="5" t="n">
-        <v>-0.36</v>
+        <v>-0.362</v>
       </c>
       <c r="H388" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I388" s="5" t="n">
-        <v>0.599</v>
+        <v>0.593</v>
       </c>
     </row>
     <row r="389">
@@ -19906,22 +19906,22 @@
         </is>
       </c>
       <c r="D389" s="5" t="n">
-        <v>0.269</v>
+        <v>0.266</v>
       </c>
       <c r="E389" s="5" t="n">
-        <v>0.91</v>
+        <v>0.916</v>
       </c>
       <c r="F389" s="5" t="n">
-        <v>-0.27</v>
+        <v>-0.266</v>
       </c>
       <c r="G389" s="5" t="n">
-        <v>-0.29</v>
+        <v>-0.288</v>
       </c>
       <c r="H389" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I389" s="5" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.798</v>
       </c>
     </row>
     <row r="390">
@@ -19945,16 +19945,16 @@
         <v>2.042</v>
       </c>
       <c r="F390" s="5" t="n">
-        <v>-0.409</v>
+        <v>-0.402</v>
       </c>
       <c r="G390" s="5" t="n">
-        <v>-0.343</v>
+        <v>-0.34</v>
       </c>
       <c r="H390" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I390" s="5" t="n">
-        <v>0.71</v>
+        <v>0.707</v>
       </c>
     </row>
     <row r="391">
@@ -19972,22 +19972,22 @@
         </is>
       </c>
       <c r="D391" s="5" t="n">
-        <v>0.078</v>
+        <v>0.077</v>
       </c>
       <c r="E391" s="5" t="n">
-        <v>0.511</v>
+        <v>0.522</v>
       </c>
       <c r="F391" s="5" t="n">
-        <v>-0.454</v>
+        <v>-0.446</v>
       </c>
       <c r="G391" s="5" t="n">
-        <v>-0.361</v>
+        <v>-0.357</v>
       </c>
       <c r="H391" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I391" s="5" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8080000000000001</v>
       </c>
     </row>
     <row r="392">
@@ -20071,19 +20071,19 @@
         </is>
       </c>
       <c r="D394" s="5" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="E394" s="5" t="n">
         <v>0.632</v>
       </c>
       <c r="F394" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.011</v>
       </c>
       <c r="G394" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="H394" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I394" s="5" t="n">
         <v>0</v>
@@ -20104,7 +20104,7 @@
         </is>
       </c>
       <c r="D395" s="5" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="E395" s="5" t="n">
         <v>0.676</v>
@@ -20467,22 +20467,22 @@
         </is>
       </c>
       <c r="D406" s="5" t="n">
-        <v>-0.21</v>
+        <v>-0.207</v>
       </c>
       <c r="E406" s="5" t="n">
-        <v>1.5</v>
+        <v>1.497</v>
       </c>
       <c r="F406" s="5" t="n">
-        <v>0.265</v>
+        <v>0.266</v>
       </c>
       <c r="G406" s="5" t="n">
-        <v>0.266</v>
+        <v>0.267</v>
       </c>
       <c r="H406" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I406" s="5" t="n">
-        <v>-0.794</v>
+        <v>-0.783</v>
       </c>
     </row>
     <row r="407">
@@ -20503,19 +20503,19 @@
         <v>-0.041</v>
       </c>
       <c r="E407" s="5" t="n">
-        <v>2.016</v>
+        <v>2.017</v>
       </c>
       <c r="F407" s="5" t="n">
-        <v>0.407</v>
+        <v>0.408</v>
       </c>
       <c r="G407" s="5" t="n">
-        <v>0.32</v>
+        <v>0.322</v>
       </c>
       <c r="H407" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I407" s="5" t="n">
-        <v>-0.71</v>
+        <v>-0.707</v>
       </c>
     </row>
     <row r="408">
@@ -20533,22 +20533,22 @@
         </is>
       </c>
       <c r="D408" s="5" t="n">
-        <v>-0.078</v>
+        <v>-0.077</v>
       </c>
       <c r="E408" s="5" t="n">
-        <v>1.626</v>
+        <v>1.625</v>
       </c>
       <c r="F408" s="5" t="n">
-        <v>0.454</v>
+        <v>0.455</v>
       </c>
       <c r="G408" s="5" t="n">
-        <v>0.338</v>
+        <v>0.34</v>
       </c>
       <c r="H408" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I408" s="5" t="n">
-        <v>-0.8149999999999999</v>
+        <v>-0.8080000000000001</v>
       </c>
     </row>
     <row r="409">
@@ -20566,22 +20566,22 @@
         </is>
       </c>
       <c r="D409" s="5" t="n">
-        <v>-0.267</v>
+        <v>-0.263</v>
       </c>
       <c r="E409" s="5" t="n">
-        <v>1.557</v>
+        <v>1.551</v>
       </c>
       <c r="F409" s="5" t="n">
-        <v>0.266</v>
+        <v>0.262</v>
       </c>
       <c r="G409" s="5" t="n">
-        <v>0.266</v>
+        <v>0.263</v>
       </c>
       <c r="H409" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I409" s="5" t="n">
-        <v>-0.8129999999999999</v>
+        <v>-0.802</v>
       </c>
     </row>
     <row r="410">
@@ -20599,22 +20599,22 @@
         </is>
       </c>
       <c r="D410" s="5" t="n">
-        <v>-0.135</v>
+        <v>-0.134</v>
       </c>
       <c r="E410" s="5" t="n">
-        <v>2.016</v>
+        <v>2.017</v>
       </c>
       <c r="F410" s="5" t="n">
-        <v>0.41</v>
+        <v>0.403</v>
       </c>
       <c r="G410" s="5" t="n">
-        <v>0.321</v>
+        <v>0.317</v>
       </c>
       <c r="H410" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I410" s="5" t="n">
-        <v>-0.4</v>
+        <v>-0.397</v>
       </c>
     </row>
     <row r="411">
@@ -20632,22 +20632,22 @@
         </is>
       </c>
       <c r="D411" s="5" t="n">
-        <v>-0.146</v>
+        <v>-0.145</v>
       </c>
       <c r="E411" s="5" t="n">
-        <v>1.63</v>
+        <v>1.619</v>
       </c>
       <c r="F411" s="5" t="n">
-        <v>0.457</v>
+        <v>0.449</v>
       </c>
       <c r="G411" s="5" t="n">
-        <v>0.339</v>
+        <v>0.335</v>
       </c>
       <c r="H411" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I411" s="5" t="n">
-        <v>-0.599</v>
+        <v>-0.593</v>
       </c>
     </row>
     <row r="412">
@@ -20677,7 +20677,7 @@
         <v>0</v>
       </c>
       <c r="H412" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I412" s="5" t="n">
         <v>-0</v>
@@ -20731,13 +20731,13 @@
         </is>
       </c>
       <c r="D414" s="5" t="n">
-        <v>-0.012</v>
+        <v>-0.011</v>
       </c>
       <c r="E414" s="5" t="n">
         <v>0.63</v>
       </c>
       <c r="F414" s="5" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="G414" s="5" t="n">
         <v>0</v>
@@ -20764,7 +20764,7 @@
         </is>
       </c>
       <c r="D415" s="5" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="E415" s="5" t="n">
         <v>0.673</v>
@@ -21127,22 +21127,22 @@
         </is>
       </c>
       <c r="D426" s="5" t="n">
-        <v>-0.214</v>
+        <v>-0.215</v>
       </c>
       <c r="E426" s="5" t="n">
-        <v>0.216</v>
+        <v>0.222</v>
       </c>
       <c r="F426" s="5" t="n">
         <v>-0.357</v>
       </c>
       <c r="G426" s="5" t="n">
-        <v>-0.358</v>
+        <v>-0.359</v>
       </c>
       <c r="H426" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I426" s="5" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.8139999999999999</v>
       </c>
     </row>
     <row r="427">
@@ -21160,22 +21160,22 @@
         </is>
       </c>
       <c r="D427" s="5" t="n">
-        <v>-0.042</v>
+        <v>-0.041</v>
       </c>
       <c r="E427" s="5" t="n">
-        <v>1.952</v>
+        <v>1.951</v>
       </c>
       <c r="F427" s="5" t="n">
-        <v>-0.553</v>
+        <v>-0.552</v>
       </c>
       <c r="G427" s="5" t="n">
-        <v>-0.432</v>
+        <v>-0.433</v>
       </c>
       <c r="H427" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I427" s="5" t="n">
-        <v>-0.712</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="428">
@@ -21193,13 +21193,13 @@
         </is>
       </c>
       <c r="D428" s="5" t="n">
-        <v>-0.079</v>
+        <v>-0.08</v>
       </c>
       <c r="E428" s="5" t="n">
-        <v>0.393</v>
+        <v>0.396</v>
       </c>
       <c r="F428" s="5" t="n">
-        <v>-0.618</v>
+        <v>-0.617</v>
       </c>
       <c r="G428" s="5" t="n">
         <v>-0.458</v>
@@ -21208,7 +21208,7 @@
         <v>-0</v>
       </c>
       <c r="I428" s="5" t="n">
-        <v>-0.822</v>
+        <v>-0.823</v>
       </c>
     </row>
     <row r="429">
@@ -21226,22 +21226,22 @@
         </is>
       </c>
       <c r="D429" s="5" t="n">
-        <v>-0.272</v>
+        <v>-0.274</v>
       </c>
       <c r="E429" s="5" t="n">
-        <v>0.268</v>
+        <v>0.276</v>
       </c>
       <c r="F429" s="5" t="n">
-        <v>-0.358</v>
+        <v>-0.354</v>
       </c>
       <c r="G429" s="5" t="n">
-        <v>-0.358</v>
+        <v>-0.355</v>
       </c>
       <c r="H429" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I429" s="5" t="n">
-        <v>-0.829</v>
+        <v>-0.833</v>
       </c>
     </row>
     <row r="430">
@@ -21265,16 +21265,16 @@
         <v>1.952</v>
       </c>
       <c r="F430" s="5" t="n">
-        <v>-0.555</v>
+        <v>-0.548</v>
       </c>
       <c r="G430" s="5" t="n">
-        <v>-0.433</v>
+        <v>-0.429</v>
       </c>
       <c r="H430" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I430" s="5" t="n">
-        <v>-0.402</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="431">
@@ -21295,13 +21295,13 @@
         <v>-0.147</v>
       </c>
       <c r="E431" s="5" t="n">
-        <v>0.389</v>
+        <v>0.4</v>
       </c>
       <c r="F431" s="5" t="n">
-        <v>-0.62</v>
+        <v>-0.612</v>
       </c>
       <c r="G431" s="5" t="n">
-        <v>-0.458</v>
+        <v>-0.454</v>
       </c>
       <c r="H431" s="5" t="n">
         <v>-0</v>
@@ -21424,13 +21424,13 @@
         </is>
       </c>
       <c r="D435" s="5" t="n">
-        <v>-0.073</v>
+        <v>-0.074</v>
       </c>
       <c r="E435" s="5" t="n">
         <v>0.671</v>
       </c>
       <c r="F435" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.012</v>
       </c>
       <c r="G435" s="5" t="n">
         <v>-0</v>
@@ -21787,22 +21787,22 @@
         </is>
       </c>
       <c r="D446" s="5" t="n">
-        <v>0.716</v>
+        <v>0.714</v>
       </c>
       <c r="E446" s="5" t="n">
-        <v>2.298</v>
+        <v>2.29</v>
       </c>
       <c r="F446" s="5" t="n">
-        <v>0.245</v>
+        <v>0.243</v>
       </c>
       <c r="G446" s="5" t="n">
-        <v>0.201</v>
+        <v>0.2</v>
       </c>
       <c r="H446" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I446" s="5" t="n">
-        <v>2.737</v>
+        <v>2.729</v>
       </c>
     </row>
     <row r="447">
@@ -21820,22 +21820,22 @@
         </is>
       </c>
       <c r="D447" s="5" t="n">
-        <v>0.34</v>
+        <v>0.339</v>
       </c>
       <c r="E447" s="5" t="n">
         <v>1.902</v>
       </c>
       <c r="F447" s="5" t="n">
-        <v>0.396</v>
+        <v>0.394</v>
       </c>
       <c r="G447" s="5" t="n">
-        <v>0.258</v>
+        <v>0.257</v>
       </c>
       <c r="H447" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I447" s="5" t="n">
-        <v>1.757</v>
+        <v>1.749</v>
       </c>
     </row>
     <row r="448">
@@ -21853,22 +21853,22 @@
         </is>
       </c>
       <c r="D448" s="5" t="n">
-        <v>0.412</v>
+        <v>0.411</v>
       </c>
       <c r="E448" s="5" t="n">
-        <v>1.314</v>
+        <v>1.31</v>
       </c>
       <c r="F448" s="5" t="n">
-        <v>0.448</v>
+        <v>0.445</v>
       </c>
       <c r="G448" s="5" t="n">
-        <v>0.278</v>
+        <v>0.277</v>
       </c>
       <c r="H448" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I448" s="5" t="n">
-        <v>2.325</v>
+        <v>2.315</v>
       </c>
     </row>
     <row r="449">
@@ -21886,13 +21886,13 @@
         </is>
       </c>
       <c r="D449" s="5" t="n">
-        <v>0.923</v>
+        <v>0.92</v>
       </c>
       <c r="E449" s="5" t="n">
-        <v>2.347</v>
+        <v>2.34</v>
       </c>
       <c r="F449" s="5" t="n">
-        <v>0.245</v>
+        <v>0.243</v>
       </c>
       <c r="G449" s="5" t="n">
         <v>0.2</v>
@@ -21901,7 +21901,7 @@
         <v>0</v>
       </c>
       <c r="I449" s="5" t="n">
-        <v>2.784</v>
+        <v>2.775</v>
       </c>
     </row>
     <row r="450">
@@ -21919,22 +21919,22 @@
         </is>
       </c>
       <c r="D450" s="5" t="n">
-        <v>0.26</v>
+        <v>0.259</v>
       </c>
       <c r="E450" s="5" t="n">
-        <v>1.903</v>
+        <v>1.902</v>
       </c>
       <c r="F450" s="5" t="n">
-        <v>0.396</v>
+        <v>0.394</v>
       </c>
       <c r="G450" s="5" t="n">
-        <v>0.258</v>
+        <v>0.257</v>
       </c>
       <c r="H450" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I450" s="5" t="n">
-        <v>2.022</v>
+        <v>2.015</v>
       </c>
     </row>
     <row r="451">
@@ -21952,22 +21952,22 @@
         </is>
       </c>
       <c r="D451" s="5" t="n">
-        <v>0.354</v>
+        <v>0.352</v>
       </c>
       <c r="E451" s="5" t="n">
-        <v>1.314</v>
+        <v>1.31</v>
       </c>
       <c r="F451" s="5" t="n">
-        <v>0.448</v>
+        <v>0.445</v>
       </c>
       <c r="G451" s="5" t="n">
-        <v>0.278</v>
+        <v>0.276</v>
       </c>
       <c r="H451" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I451" s="5" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="452">
@@ -21997,7 +21997,7 @@
         <v>0</v>
       </c>
       <c r="H452" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I452" s="5" t="n">
         <v>0</v>
@@ -22084,7 +22084,7 @@
         </is>
       </c>
       <c r="D455" s="5" t="n">
-        <v>0.247</v>
+        <v>0.246</v>
       </c>
       <c r="E455" s="5" t="n">
         <v>0.586</v>
@@ -22447,22 +22447,22 @@
         </is>
       </c>
       <c r="D466" s="5" t="n">
-        <v>0.714</v>
+        <v>0.711</v>
       </c>
       <c r="E466" s="5" t="n">
-        <v>1.905</v>
+        <v>1.9</v>
       </c>
       <c r="F466" s="5" t="n">
-        <v>0.054</v>
+        <v>0.053</v>
       </c>
       <c r="G466" s="5" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="H466" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I466" s="5" t="n">
-        <v>2.732</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="467">
@@ -22480,22 +22480,22 @@
         </is>
       </c>
       <c r="D467" s="5" t="n">
-        <v>0.34</v>
+        <v>0.339</v>
       </c>
       <c r="E467" s="5" t="n">
-        <v>1.883</v>
+        <v>1.882</v>
       </c>
       <c r="F467" s="5" t="n">
-        <v>0.102</v>
+        <v>0.1</v>
       </c>
       <c r="G467" s="5" t="n">
-        <v>0.028</v>
+        <v>0.026</v>
       </c>
       <c r="H467" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I467" s="5" t="n">
-        <v>1.756</v>
+        <v>1.748</v>
       </c>
     </row>
     <row r="468">
@@ -22513,22 +22513,22 @@
         </is>
       </c>
       <c r="D468" s="5" t="n">
-        <v>0.412</v>
+        <v>0.41</v>
       </c>
       <c r="E468" s="5" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="F468" s="5" t="n">
-        <v>0.12</v>
+        <v>0.117</v>
       </c>
       <c r="G468" s="5" t="n">
-        <v>0.035</v>
+        <v>0.033</v>
       </c>
       <c r="H468" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I468" s="5" t="n">
-        <v>2.323</v>
+        <v>2.311</v>
       </c>
     </row>
     <row r="469">
@@ -22546,22 +22546,22 @@
         </is>
       </c>
       <c r="D469" s="5" t="n">
-        <v>0.921</v>
+        <v>0.917</v>
       </c>
       <c r="E469" s="5" t="n">
-        <v>1.952</v>
+        <v>1.95</v>
       </c>
       <c r="F469" s="5" t="n">
-        <v>0.054</v>
+        <v>0.055</v>
       </c>
       <c r="G469" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="H469" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I469" s="5" t="n">
-        <v>2.779</v>
+        <v>2.766</v>
       </c>
     </row>
     <row r="470">
@@ -22579,22 +22579,22 @@
         </is>
       </c>
       <c r="D470" s="5" t="n">
-        <v>0.26</v>
+        <v>0.259</v>
       </c>
       <c r="E470" s="5" t="n">
-        <v>1.883</v>
+        <v>1.882</v>
       </c>
       <c r="F470" s="5" t="n">
-        <v>0.101</v>
+        <v>0.103</v>
       </c>
       <c r="G470" s="5" t="n">
-        <v>0.027</v>
+        <v>0.028</v>
       </c>
       <c r="H470" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I470" s="5" t="n">
-        <v>2.022</v>
+        <v>2.014</v>
       </c>
     </row>
     <row r="471">
@@ -22612,22 +22612,22 @@
         </is>
       </c>
       <c r="D471" s="5" t="n">
-        <v>0.353</v>
+        <v>0.352</v>
       </c>
       <c r="E471" s="5" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="F471" s="5" t="n">
-        <v>0.119</v>
+        <v>0.12</v>
       </c>
       <c r="G471" s="5" t="n">
-        <v>0.034</v>
+        <v>0.035</v>
       </c>
       <c r="H471" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I471" s="5" t="n">
-        <v>2.507</v>
+        <v>2.495</v>
       </c>
     </row>
     <row r="472">
@@ -22657,7 +22657,7 @@
         <v>0</v>
       </c>
       <c r="H472" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I472" s="5" t="n">
         <v>0</v>
@@ -22690,7 +22690,7 @@
         <v>-0</v>
       </c>
       <c r="H473" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I473" s="5" t="n">
         <v>0</v>
@@ -22711,7 +22711,7 @@
         </is>
       </c>
       <c r="D474" s="5" t="n">
-        <v>0.04</v>
+        <v>0.039</v>
       </c>
       <c r="E474" s="5" t="n">
         <v>0.55</v>
@@ -22744,7 +22744,7 @@
         </is>
       </c>
       <c r="D475" s="5" t="n">
-        <v>0.246</v>
+        <v>0.245</v>
       </c>
       <c r="E475" s="5" t="n">
         <v>0.586</v>
@@ -22756,7 +22756,7 @@
         <v>-0</v>
       </c>
       <c r="H475" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I475" s="5" t="n">
         <v>0</v>
@@ -22786,7 +22786,7 @@
         <v>-0</v>
       </c>
       <c r="G476" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H476" s="5" t="n">
         <v>0</v>
@@ -22852,7 +22852,7 @@
         <v>-0</v>
       </c>
       <c r="G478" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H478" s="5" t="n">
         <v>-0</v>
@@ -22951,7 +22951,7 @@
         <v>-0</v>
       </c>
       <c r="G481" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H481" s="5" t="n">
         <v>-0</v>
@@ -23017,7 +23017,7 @@
         <v>-0</v>
       </c>
       <c r="G483" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H483" s="5" t="n">
         <v>-0</v>
@@ -23107,22 +23107,22 @@
         </is>
       </c>
       <c r="D486" s="5" t="n">
-        <v>-0.716</v>
+        <v>-0.713</v>
       </c>
       <c r="E486" s="5" t="n">
-        <v>0.116</v>
+        <v>0.121</v>
       </c>
       <c r="F486" s="5" t="n">
-        <v>-0.057</v>
+        <v>-0.056</v>
       </c>
       <c r="G486" s="5" t="n">
-        <v>-0.031</v>
+        <v>-0.029</v>
       </c>
       <c r="H486" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I486" s="5" t="n">
-        <v>-2.728</v>
+        <v>-2.716</v>
       </c>
     </row>
     <row r="487">
@@ -23140,22 +23140,22 @@
         </is>
       </c>
       <c r="D487" s="5" t="n">
-        <v>-0.26</v>
+        <v>-0.259</v>
       </c>
       <c r="E487" s="5" t="n">
-        <v>1.596</v>
+        <v>1.597</v>
       </c>
       <c r="F487" s="5" t="n">
-        <v>-0.102</v>
+        <v>-0.099</v>
       </c>
       <c r="G487" s="5" t="n">
-        <v>-0.047</v>
+        <v>-0.046</v>
       </c>
       <c r="H487" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I487" s="5" t="n">
-        <v>-2.022</v>
+        <v>-2.014</v>
       </c>
     </row>
     <row r="488">
@@ -23173,22 +23173,22 @@
         </is>
       </c>
       <c r="D488" s="5" t="n">
-        <v>-0.354</v>
+        <v>-0.352</v>
       </c>
       <c r="E488" s="5" t="n">
-        <v>0.899</v>
+        <v>0.901</v>
       </c>
       <c r="F488" s="5" t="n">
-        <v>-0.118</v>
+        <v>-0.115</v>
       </c>
       <c r="G488" s="5" t="n">
-        <v>-0.054</v>
+        <v>-0.052</v>
       </c>
       <c r="H488" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I488" s="5" t="n">
-        <v>-2.507</v>
+        <v>-2.495</v>
       </c>
     </row>
     <row r="489">
@@ -23206,22 +23206,22 @@
         </is>
       </c>
       <c r="D489" s="5" t="n">
-        <v>-0.919</v>
+        <v>-0.915</v>
       </c>
       <c r="E489" s="5" t="n">
-        <v>0.162</v>
+        <v>0.165</v>
       </c>
       <c r="F489" s="5" t="n">
         <v>-0.057</v>
       </c>
       <c r="G489" s="5" t="n">
-        <v>-0.03</v>
+        <v>-0.031</v>
       </c>
       <c r="H489" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I489" s="5" t="n">
-        <v>-2.782</v>
+        <v>-2.769</v>
       </c>
     </row>
     <row r="490">
@@ -23239,22 +23239,22 @@
         </is>
       </c>
       <c r="D490" s="5" t="n">
-        <v>-0.34</v>
+        <v>-0.339</v>
       </c>
       <c r="E490" s="5" t="n">
-        <v>1.596</v>
+        <v>1.597</v>
       </c>
       <c r="F490" s="5" t="n">
-        <v>-0.101</v>
+        <v>-0.102</v>
       </c>
       <c r="G490" s="5" t="n">
-        <v>-0.047</v>
+        <v>-0.048</v>
       </c>
       <c r="H490" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I490" s="5" t="n">
-        <v>-1.756</v>
+        <v>-1.748</v>
       </c>
     </row>
     <row r="491">
@@ -23272,22 +23272,22 @@
         </is>
       </c>
       <c r="D491" s="5" t="n">
-        <v>-0.412</v>
+        <v>-0.41</v>
       </c>
       <c r="E491" s="5" t="n">
-        <v>0.9</v>
+        <v>0.897</v>
       </c>
       <c r="F491" s="5" t="n">
-        <v>-0.117</v>
+        <v>-0.118</v>
       </c>
       <c r="G491" s="5" t="n">
-        <v>-0.053</v>
+        <v>-0.054</v>
       </c>
       <c r="H491" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I491" s="5" t="n">
-        <v>-2.323</v>
+        <v>-2.311</v>
       </c>
     </row>
     <row r="492">
@@ -23350,7 +23350,7 @@
         <v>0</v>
       </c>
       <c r="H493" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I493" s="5" t="n">
         <v>-0</v>
@@ -23371,7 +23371,7 @@
         </is>
       </c>
       <c r="D494" s="5" t="n">
-        <v>-0.04</v>
+        <v>-0.039</v>
       </c>
       <c r="E494" s="5" t="n">
         <v>0.532</v>
@@ -23404,7 +23404,7 @@
         </is>
       </c>
       <c r="D495" s="5" t="n">
-        <v>-0.246</v>
+        <v>-0.245</v>
       </c>
       <c r="E495" s="5" t="n">
         <v>0.57</v>
@@ -23416,7 +23416,7 @@
         <v>0</v>
       </c>
       <c r="H495" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I495" s="5" t="n">
         <v>-0</v>
@@ -23446,7 +23446,7 @@
         <v>0</v>
       </c>
       <c r="G496" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H496" s="5" t="n">
         <v>0</v>
@@ -23512,7 +23512,7 @@
         <v>0</v>
       </c>
       <c r="G498" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H498" s="5" t="n">
         <v>-0</v>
@@ -23611,7 +23611,7 @@
         <v>0</v>
       </c>
       <c r="G501" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H501" s="5" t="n">
         <v>-0</v>
@@ -23677,7 +23677,7 @@
         <v>0</v>
       </c>
       <c r="G503" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H503" s="5" t="n">
         <v>-0</v>
@@ -23767,13 +23767,13 @@
         </is>
       </c>
       <c r="D506" s="5" t="n">
-        <v>-0.718</v>
+        <v>-0.716</v>
       </c>
       <c r="E506" s="5" t="n">
-        <v>-0.277</v>
+        <v>-0.269</v>
       </c>
       <c r="F506" s="5" t="n">
-        <v>-0.248</v>
+        <v>-0.246</v>
       </c>
       <c r="G506" s="5" t="n">
         <v>-0.221</v>
@@ -23782,7 +23782,7 @@
         <v>-0</v>
       </c>
       <c r="I506" s="5" t="n">
-        <v>-2.733</v>
+        <v>-2.725</v>
       </c>
     </row>
     <row r="507">
@@ -23800,22 +23800,22 @@
         </is>
       </c>
       <c r="D507" s="5" t="n">
-        <v>-0.26</v>
+        <v>-0.259</v>
       </c>
       <c r="E507" s="5" t="n">
-        <v>1.576</v>
+        <v>1.577</v>
       </c>
       <c r="F507" s="5" t="n">
-        <v>-0.395</v>
+        <v>-0.393</v>
       </c>
       <c r="G507" s="5" t="n">
-        <v>-0.278</v>
+        <v>-0.277</v>
       </c>
       <c r="H507" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I507" s="5" t="n">
-        <v>-2.022</v>
+        <v>-2.015</v>
       </c>
     </row>
     <row r="508">
@@ -23833,22 +23833,22 @@
         </is>
       </c>
       <c r="D508" s="5" t="n">
-        <v>-0.354</v>
+        <v>-0.353</v>
       </c>
       <c r="E508" s="5" t="n">
-        <v>0.521</v>
+        <v>0.526</v>
       </c>
       <c r="F508" s="5" t="n">
-        <v>-0.446</v>
+        <v>-0.443</v>
       </c>
       <c r="G508" s="5" t="n">
-        <v>-0.297</v>
+        <v>-0.296</v>
       </c>
       <c r="H508" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I508" s="5" t="n">
-        <v>-2.51</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="509">
@@ -23866,22 +23866,22 @@
         </is>
       </c>
       <c r="D509" s="5" t="n">
-        <v>-0.921</v>
+        <v>-0.918</v>
       </c>
       <c r="E509" s="5" t="n">
-        <v>-0.232</v>
+        <v>-0.225</v>
       </c>
       <c r="F509" s="5" t="n">
-        <v>-0.248</v>
+        <v>-0.246</v>
       </c>
       <c r="G509" s="5" t="n">
-        <v>-0.221</v>
+        <v>-0.22</v>
       </c>
       <c r="H509" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I509" s="5" t="n">
-        <v>-2.787</v>
+        <v>-2.779</v>
       </c>
     </row>
     <row r="510">
@@ -23899,22 +23899,22 @@
         </is>
       </c>
       <c r="D510" s="5" t="n">
-        <v>-0.34</v>
+        <v>-0.339</v>
       </c>
       <c r="E510" s="5" t="n">
-        <v>1.576</v>
+        <v>1.577</v>
       </c>
       <c r="F510" s="5" t="n">
-        <v>-0.396</v>
+        <v>-0.393</v>
       </c>
       <c r="G510" s="5" t="n">
-        <v>-0.277</v>
+        <v>-0.276</v>
       </c>
       <c r="H510" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I510" s="5" t="n">
-        <v>-1.756</v>
+        <v>-1.749</v>
       </c>
     </row>
     <row r="511">
@@ -23932,22 +23932,22 @@
         </is>
       </c>
       <c r="D511" s="5" t="n">
-        <v>-0.412</v>
+        <v>-0.411</v>
       </c>
       <c r="E511" s="5" t="n">
-        <v>0.521</v>
+        <v>0.524</v>
       </c>
       <c r="F511" s="5" t="n">
-        <v>-0.446</v>
+        <v>-0.443</v>
       </c>
       <c r="G511" s="5" t="n">
-        <v>-0.297</v>
+        <v>-0.295</v>
       </c>
       <c r="H511" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I511" s="5" t="n">
-        <v>-2.325</v>
+        <v>-2.315</v>
       </c>
     </row>
     <row r="512">
@@ -24064,7 +24064,7 @@
         </is>
       </c>
       <c r="D515" s="5" t="n">
-        <v>-0.247</v>
+        <v>-0.246</v>
       </c>
       <c r="E515" s="5" t="n">
         <v>0.569</v>
@@ -24427,22 +24427,22 @@
         </is>
       </c>
       <c r="D526" s="5" t="n">
-        <v>0.216</v>
+        <v>0.217</v>
       </c>
       <c r="E526" s="5" t="n">
-        <v>1.993</v>
+        <v>1.986</v>
       </c>
       <c r="F526" s="5" t="n">
         <v>0.361</v>
       </c>
       <c r="G526" s="5" t="n">
-        <v>0.342</v>
+        <v>0.343</v>
       </c>
       <c r="H526" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I526" s="5" t="n">
-        <v>0.83</v>
+        <v>0.834</v>
       </c>
     </row>
     <row r="527">
@@ -24466,16 +24466,16 @@
         <v>1.818</v>
       </c>
       <c r="F527" s="5" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="G527" s="5" t="n">
-        <v>0.42</v>
+        <v>0.421</v>
       </c>
       <c r="H527" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I527" s="5" t="n">
-        <v>0.435</v>
+        <v>0.433</v>
       </c>
     </row>
     <row r="528">
@@ -24493,22 +24493,22 @@
         </is>
       </c>
       <c r="D528" s="5" t="n">
-        <v>0.144</v>
+        <v>0.145</v>
       </c>
       <c r="E528" s="5" t="n">
-        <v>1.608</v>
+        <v>1.605</v>
       </c>
       <c r="F528" s="5" t="n">
-        <v>0.632</v>
+        <v>0.631</v>
       </c>
       <c r="G528" s="5" t="n">
-        <v>0.446</v>
+        <v>0.447</v>
       </c>
       <c r="H528" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I528" s="5" t="n">
-        <v>0.636</v>
+        <v>0.637</v>
       </c>
     </row>
     <row r="529">
@@ -24526,22 +24526,22 @@
         </is>
       </c>
       <c r="D529" s="5" t="n">
-        <v>0.28</v>
+        <v>0.282</v>
       </c>
       <c r="E529" s="5" t="n">
-        <v>2.042</v>
+        <v>2.033</v>
       </c>
       <c r="F529" s="5" t="n">
-        <v>0.362</v>
+        <v>0.358</v>
       </c>
       <c r="G529" s="5" t="n">
-        <v>0.343</v>
+        <v>0.34</v>
       </c>
       <c r="H529" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I529" s="5" t="n">
-        <v>0.841</v>
+        <v>0.846</v>
       </c>
     </row>
     <row r="530">
@@ -24565,16 +24565,16 @@
         <v>1.818</v>
       </c>
       <c r="F530" s="5" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="G530" s="5" t="n">
-        <v>0.42</v>
+        <v>0.416</v>
       </c>
       <c r="H530" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I530" s="5" t="n">
-        <v>0.701</v>
+        <v>0.699</v>
       </c>
     </row>
     <row r="531">
@@ -24592,16 +24592,16 @@
         </is>
       </c>
       <c r="D531" s="5" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="E531" s="5" t="n">
-        <v>1.612</v>
+        <v>1.601</v>
       </c>
       <c r="F531" s="5" t="n">
-        <v>0.635</v>
+        <v>0.626</v>
       </c>
       <c r="G531" s="5" t="n">
-        <v>0.447</v>
+        <v>0.442</v>
       </c>
       <c r="H531" s="5" t="n">
         <v>0</v>
@@ -25087,22 +25087,22 @@
         </is>
       </c>
       <c r="D546" s="5" t="n">
-        <v>0.212</v>
+        <v>0.209</v>
       </c>
       <c r="E546" s="5" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="F546" s="5" t="n">
-        <v>-0.273</v>
+        <v>-0.274</v>
       </c>
       <c r="G546" s="5" t="n">
-        <v>-0.294</v>
+        <v>-0.295</v>
       </c>
       <c r="H546" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I546" s="5" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.803</v>
       </c>
     </row>
     <row r="547">
@@ -25120,7 +25120,7 @@
         </is>
       </c>
       <c r="D547" s="5" t="n">
-        <v>0.13</v>
+        <v>0.129</v>
       </c>
       <c r="E547" s="5" t="n">
         <v>1.752</v>
@@ -25129,13 +25129,13 @@
         <v>-0.415</v>
       </c>
       <c r="G547" s="5" t="n">
-        <v>-0.347</v>
+        <v>-0.349</v>
       </c>
       <c r="H547" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I547" s="5" t="n">
-        <v>0.433</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="548">
@@ -25153,22 +25153,22 @@
         </is>
       </c>
       <c r="D548" s="5" t="n">
-        <v>0.143</v>
+        <v>0.142</v>
       </c>
       <c r="E548" s="5" t="n">
-        <v>0.351</v>
+        <v>0.352</v>
       </c>
       <c r="F548" s="5" t="n">
         <v>-0.461</v>
       </c>
       <c r="G548" s="5" t="n">
-        <v>-0.365</v>
+        <v>-0.367</v>
       </c>
       <c r="H548" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I548" s="5" t="n">
-        <v>0.629</v>
+        <v>0.622</v>
       </c>
     </row>
     <row r="549">
@@ -25186,22 +25186,22 @@
         </is>
       </c>
       <c r="D549" s="5" t="n">
-        <v>0.275</v>
+        <v>0.271</v>
       </c>
       <c r="E549" s="5" t="n">
-        <v>0.728</v>
+        <v>0.734</v>
       </c>
       <c r="F549" s="5" t="n">
-        <v>-0.275</v>
+        <v>-0.27</v>
       </c>
       <c r="G549" s="5" t="n">
-        <v>-0.294</v>
+        <v>-0.291</v>
       </c>
       <c r="H549" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I549" s="5" t="n">
-        <v>0.825</v>
+        <v>0.8139999999999999</v>
       </c>
     </row>
     <row r="550">
@@ -25219,22 +25219,22 @@
         </is>
       </c>
       <c r="D550" s="5" t="n">
-        <v>0.05</v>
+        <v>0.049</v>
       </c>
       <c r="E550" s="5" t="n">
         <v>1.753</v>
       </c>
       <c r="F550" s="5" t="n">
-        <v>-0.417</v>
+        <v>-0.41</v>
       </c>
       <c r="G550" s="5" t="n">
-        <v>-0.348</v>
+        <v>-0.344</v>
       </c>
       <c r="H550" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I550" s="5" t="n">
-        <v>0.699</v>
+        <v>0.696</v>
       </c>
     </row>
     <row r="551">
@@ -25252,22 +25252,22 @@
         </is>
       </c>
       <c r="D551" s="5" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E551" s="5" t="n">
-        <v>0.347</v>
+        <v>0.358</v>
       </c>
       <c r="F551" s="5" t="n">
-        <v>-0.463</v>
+        <v>-0.455</v>
       </c>
       <c r="G551" s="5" t="n">
-        <v>-0.366</v>
+        <v>-0.362</v>
       </c>
       <c r="H551" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I551" s="5" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8070000000000001</v>
       </c>
     </row>
     <row r="552">
@@ -25363,7 +25363,7 @@
         <v>-0</v>
       </c>
       <c r="H554" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I554" s="5" t="n">
         <v>0</v>
@@ -25384,7 +25384,7 @@
         </is>
       </c>
       <c r="D555" s="5" t="n">
-        <v>0.073</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="E555" s="5" t="n">
         <v>0.579</v>
@@ -25747,22 +25747,22 @@
         </is>
       </c>
       <c r="D566" s="5" t="n">
-        <v>-0.213</v>
+        <v>-0.211</v>
       </c>
       <c r="E566" s="5" t="n">
-        <v>1.338</v>
+        <v>1.335</v>
       </c>
       <c r="F566" s="5" t="n">
         <v>0.271</v>
       </c>
       <c r="G566" s="5" t="n">
-        <v>0.273</v>
+        <v>0.275</v>
       </c>
       <c r="H566" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I566" s="5" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.799</v>
       </c>
     </row>
     <row r="567">
@@ -25783,19 +25783,19 @@
         <v>-0.049</v>
       </c>
       <c r="E567" s="5" t="n">
-        <v>1.726</v>
+        <v>1.727</v>
       </c>
       <c r="F567" s="5" t="n">
-        <v>0.415</v>
+        <v>0.416</v>
       </c>
       <c r="G567" s="5" t="n">
-        <v>0.328</v>
+        <v>0.33</v>
       </c>
       <c r="H567" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I567" s="5" t="n">
-        <v>-0.699</v>
+        <v>-0.696</v>
       </c>
     </row>
     <row r="568">
@@ -25813,22 +25813,22 @@
         </is>
       </c>
       <c r="D568" s="5" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="E568" s="5" t="n">
-        <v>1.484</v>
+        <v>1.483</v>
       </c>
       <c r="F568" s="5" t="n">
         <v>0.463</v>
       </c>
       <c r="G568" s="5" t="n">
-        <v>0.346</v>
+        <v>0.348</v>
       </c>
       <c r="H568" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I568" s="5" t="n">
-        <v>-0.8129999999999999</v>
+        <v>-0.806</v>
       </c>
     </row>
     <row r="569">
@@ -25846,22 +25846,22 @@
         </is>
       </c>
       <c r="D569" s="5" t="n">
-        <v>-0.272</v>
+        <v>-0.269</v>
       </c>
       <c r="E569" s="5" t="n">
-        <v>1.387</v>
+        <v>1.381</v>
       </c>
       <c r="F569" s="5" t="n">
-        <v>0.272</v>
+        <v>0.268</v>
       </c>
       <c r="G569" s="5" t="n">
-        <v>0.273</v>
+        <v>0.27</v>
       </c>
       <c r="H569" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I569" s="5" t="n">
-        <v>-0.828</v>
+        <v>-0.8179999999999999</v>
       </c>
     </row>
     <row r="570">
@@ -25879,22 +25879,22 @@
         </is>
       </c>
       <c r="D570" s="5" t="n">
-        <v>-0.13</v>
+        <v>-0.129</v>
       </c>
       <c r="E570" s="5" t="n">
-        <v>1.726</v>
+        <v>1.727</v>
       </c>
       <c r="F570" s="5" t="n">
-        <v>0.418</v>
+        <v>0.411</v>
       </c>
       <c r="G570" s="5" t="n">
-        <v>0.329</v>
+        <v>0.325</v>
       </c>
       <c r="H570" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I570" s="5" t="n">
-        <v>-0.433</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="571">
@@ -25912,22 +25912,22 @@
         </is>
       </c>
       <c r="D571" s="5" t="n">
-        <v>-0.143</v>
+        <v>-0.142</v>
       </c>
       <c r="E571" s="5" t="n">
-        <v>1.488</v>
+        <v>1.477</v>
       </c>
       <c r="F571" s="5" t="n">
-        <v>0.465</v>
+        <v>0.457</v>
       </c>
       <c r="G571" s="5" t="n">
-        <v>0.347</v>
+        <v>0.343</v>
       </c>
       <c r="H571" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I571" s="5" t="n">
-        <v>-0.629</v>
+        <v>-0.622</v>
       </c>
     </row>
     <row r="572">
@@ -25957,7 +25957,7 @@
         <v>0</v>
       </c>
       <c r="H572" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I572" s="5" t="n">
         <v>-0</v>
@@ -26044,7 +26044,7 @@
         </is>
       </c>
       <c r="D575" s="5" t="n">
-        <v>-0.073</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="E575" s="5" t="n">
         <v>0.576</v>
@@ -26245,7 +26245,7 @@
         <v>-0</v>
       </c>
       <c r="E581" s="5" t="n">
-        <v>0.239</v>
+        <v>0.238</v>
       </c>
       <c r="F581" s="5" t="n">
         <v>0</v>
@@ -26377,7 +26377,7 @@
         <v>-0</v>
       </c>
       <c r="E585" s="5" t="n">
-        <v>0.298</v>
+        <v>0.297</v>
       </c>
       <c r="F585" s="5" t="n">
         <v>0</v>
@@ -26407,22 +26407,22 @@
         </is>
       </c>
       <c r="D586" s="5" t="n">
-        <v>-0.218</v>
+        <v>-0.219</v>
       </c>
       <c r="E586" s="5" t="n">
-        <v>0.028</v>
+        <v>0.035</v>
       </c>
       <c r="F586" s="5" t="n">
         <v>-0.364</v>
       </c>
       <c r="G586" s="5" t="n">
-        <v>-0.363</v>
+        <v>-0.364</v>
       </c>
       <c r="H586" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I586" s="5" t="n">
-        <v>-0.826</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="587">
@@ -26446,16 +26446,16 @@
         <v>1.66</v>
       </c>
       <c r="F587" s="5" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="G587" s="5" t="n">
-        <v>-0.439</v>
+        <v>-0.44</v>
       </c>
       <c r="H587" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I587" s="5" t="n">
-        <v>-0.701</v>
+        <v>-0.699</v>
       </c>
     </row>
     <row r="588">
@@ -26473,16 +26473,16 @@
         </is>
       </c>
       <c r="D588" s="5" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="E588" s="5" t="n">
-        <v>0.227</v>
+        <v>0.23</v>
       </c>
       <c r="F588" s="5" t="n">
-        <v>-0.63</v>
+        <v>-0.629</v>
       </c>
       <c r="G588" s="5" t="n">
-        <v>-0.465</v>
+        <v>-0.466</v>
       </c>
       <c r="H588" s="5" t="n">
         <v>-0</v>
@@ -26506,22 +26506,22 @@
         </is>
       </c>
       <c r="D589" s="5" t="n">
-        <v>-0.278</v>
+        <v>-0.28</v>
       </c>
       <c r="E589" s="5" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.081</v>
       </c>
       <c r="F589" s="5" t="n">
-        <v>-0.365</v>
+        <v>-0.361</v>
       </c>
       <c r="G589" s="5" t="n">
-        <v>-0.363</v>
+        <v>-0.36</v>
       </c>
       <c r="H589" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I589" s="5" t="n">
-        <v>-0.845</v>
+        <v>-0.849</v>
       </c>
     </row>
     <row r="590">
@@ -26545,16 +26545,16 @@
         <v>1.661</v>
       </c>
       <c r="F590" s="5" t="n">
-        <v>-0.5659999999999999</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="G590" s="5" t="n">
-        <v>-0.44</v>
+        <v>-0.436</v>
       </c>
       <c r="H590" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I590" s="5" t="n">
-        <v>-0.435</v>
+        <v>-0.433</v>
       </c>
     </row>
     <row r="591">
@@ -26575,13 +26575,13 @@
         <v>-0.145</v>
       </c>
       <c r="E591" s="5" t="n">
-        <v>0.223</v>
+        <v>0.234</v>
       </c>
       <c r="F591" s="5" t="n">
-        <v>-0.633</v>
+        <v>-0.624</v>
       </c>
       <c r="G591" s="5" t="n">
-        <v>-0.466</v>
+        <v>-0.461</v>
       </c>
       <c r="H591" s="5" t="n">
         <v>-0</v>
@@ -33866,7 +33866,7 @@
         <v>27</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H34" s="10" t="n">
         <v>19</v>
@@ -33922,7 +33922,7 @@
         <v>20</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H36" s="10" t="n">
         <v>16</v>
@@ -34034,7 +34034,7 @@
         <v>20</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="H40" s="10" t="n">
         <v>24</v>
@@ -34317,7 +34317,7 @@
         <v>24</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51">
@@ -34597,7 +34597,7 @@
         <v>27</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61">
@@ -34653,7 +34653,7 @@
         <v>25</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63">
@@ -34821,7 +34821,7 @@
         <v>24</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="69">
@@ -35039,7 +35039,7 @@
         <v>20</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G76" s="10" t="n">
         <v>26</v>
@@ -35095,7 +35095,7 @@
         <v>23</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G78" s="10" t="n">
         <v>27</v>
@@ -35675,7 +35675,7 @@
         <v>-1.518</v>
       </c>
       <c r="E100" s="9" t="n">
-        <v>-0.63</v>
+        <v>-0.629</v>
       </c>
       <c r="F100" s="9" t="n">
         <v>-0.72</v>
@@ -36211,7 +36211,7 @@
         <v>46</v>
       </c>
       <c r="G119" s="10" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H119" s="10" t="n">
         <v>42</v>
@@ -36323,7 +36323,7 @@
         <v>46</v>
       </c>
       <c r="G123" s="10" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H123" s="10" t="n">
         <v>51</v>
@@ -36606,7 +36606,7 @@
         <v>51</v>
       </c>
       <c r="H133" s="10" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="134">
@@ -36886,7 +36886,7 @@
         <v>57</v>
       </c>
       <c r="H143" s="10" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="144">
@@ -36942,7 +36942,7 @@
         <v>53</v>
       </c>
       <c r="H145" s="10" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
     </row>
     <row r="146">
@@ -37054,7 +37054,7 @@
         <v>51</v>
       </c>
       <c r="H149" s="10" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="150">
@@ -37110,7 +37110,7 @@
         <v>51</v>
       </c>
       <c r="H151" s="10" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="152">
@@ -37328,7 +37328,7 @@
         <v>46</v>
       </c>
       <c r="F159" s="10" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G159" s="10" t="n">
         <v>55</v>
@@ -37384,7 +37384,7 @@
         <v>49</v>
       </c>
       <c r="F161" s="10" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G161" s="10" t="n">
         <v>57</v>

--- a/002/002_REACCIONES_BASES_3.0.xlsx
+++ b/002/002_REACCIONES_BASES_3.0.xlsx
@@ -1896,7 +1896,7 @@
         <v>0.499</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0.759</v>
+        <v>0.758</v>
       </c>
       <c r="F46" s="5" t="n">
         <v>0.105</v>
@@ -1908,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>1.904</v>
+        <v>1.903</v>
       </c>
     </row>
     <row r="47">
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>1.316</v>
+        <v>1.315</v>
       </c>
     </row>
     <row r="48">
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>0.267</v>
+        <v>0.266</v>
       </c>
       <c r="E48" s="5" t="n">
         <v>0.143</v>
@@ -1974,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>1.682</v>
+        <v>1.681</v>
       </c>
     </row>
     <row r="49">
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>0.642</v>
+        <v>0.641</v>
       </c>
       <c r="E49" s="5" t="n">
         <v>0.76</v>
@@ -2007,7 +2007,7 @@
         <v>0</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>1.939</v>
+        <v>1.938</v>
       </c>
     </row>
     <row r="50">
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>1.316</v>
+        <v>1.315</v>
       </c>
     </row>
     <row r="51">
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>0.267</v>
+        <v>0.266</v>
       </c>
       <c r="E51" s="5" t="n">
         <v>0.144</v>
@@ -2073,7 +2073,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>1.682</v>
+        <v>1.681</v>
       </c>
     </row>
     <row r="52">
@@ -2562,7 +2562,7 @@
         <v>0.222</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.223</v>
+        <v>0.224</v>
       </c>
       <c r="H66" s="5" t="n">
         <v>0</v>
@@ -2592,7 +2592,7 @@
         <v>0.023</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>0.342</v>
+        <v>0.343</v>
       </c>
       <c r="G67" s="5" t="n">
         <v>0.269</v>
@@ -2655,7 +2655,7 @@
         <v>0.004</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>0.454</v>
+        <v>0.455</v>
       </c>
       <c r="F69" s="5" t="n">
         <v>0.22</v>
@@ -2721,10 +2721,10 @@
         <v>0.001</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>0.434</v>
+        <v>0.435</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>0.378</v>
+        <v>0.379</v>
       </c>
       <c r="G71" s="5" t="n">
         <v>0.281</v>
@@ -3216,7 +3216,7 @@
         <v>-0.499</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>-0.759</v>
+        <v>-0.758</v>
       </c>
       <c r="F86" s="5" t="n">
         <v>-0.105</v>
@@ -3228,7 +3228,7 @@
         <v>-0</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>-1.904</v>
+        <v>-1.903</v>
       </c>
     </row>
     <row r="87">
@@ -3261,7 +3261,7 @@
         <v>-0</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>-1.316</v>
+        <v>-1.315</v>
       </c>
     </row>
     <row r="88">
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="D88" s="5" t="n">
-        <v>-0.267</v>
+        <v>-0.266</v>
       </c>
       <c r="E88" s="5" t="n">
         <v>-0.143</v>
@@ -3294,7 +3294,7 @@
         <v>-0</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>-1.682</v>
+        <v>-1.681</v>
       </c>
     </row>
     <row r="89">
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="D89" s="5" t="n">
-        <v>-0.642</v>
+        <v>-0.641</v>
       </c>
       <c r="E89" s="5" t="n">
         <v>-0.76</v>
@@ -3327,7 +3327,7 @@
         <v>-0</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>-1.939</v>
+        <v>-1.938</v>
       </c>
     </row>
     <row r="90">
@@ -3360,7 +3360,7 @@
         <v>-0</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>-1.316</v>
+        <v>-1.315</v>
       </c>
     </row>
     <row r="91">
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="D91" s="5" t="n">
-        <v>-0.267</v>
+        <v>-0.266</v>
       </c>
       <c r="E91" s="5" t="n">
         <v>-0.144</v>
@@ -3393,7 +3393,7 @@
         <v>-0</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>-1.682</v>
+        <v>-1.681</v>
       </c>
     </row>
     <row r="92">
@@ -3882,7 +3882,7 @@
         <v>-0.222</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>-0.223</v>
+        <v>-0.224</v>
       </c>
       <c r="H106" s="5" t="n">
         <v>-0</v>
@@ -3912,7 +3912,7 @@
         <v>-0.023</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>-0.342</v>
+        <v>-0.343</v>
       </c>
       <c r="G107" s="5" t="n">
         <v>-0.269</v>
@@ -3975,7 +3975,7 @@
         <v>-0.004</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>-0.454</v>
+        <v>-0.455</v>
       </c>
       <c r="F109" s="5" t="n">
         <v>-0.22</v>
@@ -4041,10 +4041,10 @@
         <v>-0.001</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>-0.434</v>
+        <v>-0.435</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>-0.378</v>
+        <v>-0.379</v>
       </c>
       <c r="G111" s="5" t="n">
         <v>-0.281</v>
@@ -7282,7 +7282,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>1.909</v>
+        <v>1.908</v>
       </c>
     </row>
     <row r="7">
@@ -7348,7 +7348,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>1.581</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="9">
@@ -7381,7 +7381,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>1.94</v>
+        <v>1.939</v>
       </c>
     </row>
     <row r="10">
@@ -7414,7 +7414,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>1.464</v>
+        <v>1.463</v>
       </c>
     </row>
     <row r="11">
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.235</v>
+        <v>0.234</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>1.294</v>
@@ -7447,7 +7447,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>1.786</v>
+        <v>1.785</v>
       </c>
     </row>
     <row r="12">
@@ -7942,7 +7942,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>1.903</v>
+        <v>1.902</v>
       </c>
     </row>
     <row r="27">
@@ -7975,7 +7975,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>1.168</v>
+        <v>1.167</v>
       </c>
     </row>
     <row r="28">
@@ -8008,7 +8008,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>1.578</v>
+        <v>1.577</v>
       </c>
     </row>
     <row r="29">
@@ -8026,10 +8026,10 @@
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>0.642</v>
+        <v>0.641</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>1.799</v>
+        <v>1.798</v>
       </c>
       <c r="F29" s="5" t="n">
         <v>0.038</v>
@@ -8041,7 +8041,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>1.933</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="30">
@@ -8107,7 +8107,7 @@
         <v>-0</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>1.783</v>
+        <v>1.782</v>
       </c>
     </row>
     <row r="32">
@@ -8137,7 +8137,7 @@
         <v>0</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I32" s="5" t="n">
         <v>0</v>
@@ -8266,7 +8266,7 @@
         <v>-0</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H36" s="5" t="n">
         <v>0</v>
@@ -8299,7 +8299,7 @@
         <v>-0</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H37" s="5" t="n">
         <v>-0</v>
@@ -8332,7 +8332,7 @@
         <v>-0</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H38" s="5" t="n">
         <v>-0</v>
@@ -8365,7 +8365,7 @@
         <v>-0</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H39" s="5" t="n">
         <v>-0</v>
@@ -8497,7 +8497,7 @@
         <v>-0</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H43" s="5" t="n">
         <v>-0</v>
@@ -8668,7 +8668,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>-1.783</v>
+        <v>-1.782</v>
       </c>
     </row>
     <row r="49">
@@ -8734,7 +8734,7 @@
         <v>-0</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>-1.168</v>
+        <v>-1.167</v>
       </c>
     </row>
     <row r="51">
@@ -8767,7 +8767,7 @@
         <v>-0</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>-1.578</v>
+        <v>-1.577</v>
       </c>
     </row>
     <row r="52">
@@ -8926,7 +8926,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H56" s="5" t="n">
         <v>0</v>
@@ -8959,7 +8959,7 @@
         <v>0</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H57" s="5" t="n">
         <v>-0</v>
@@ -8992,7 +8992,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H58" s="5" t="n">
         <v>-0</v>
@@ -9025,7 +9025,7 @@
         <v>0</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H59" s="5" t="n">
         <v>-0</v>
@@ -9124,7 +9124,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H62" s="5" t="n">
         <v>-0</v>
@@ -9157,7 +9157,7 @@
         <v>0</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H63" s="5" t="n">
         <v>-0</v>
@@ -9262,7 +9262,7 @@
         <v>-0</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>-1.905</v>
+        <v>-1.904</v>
       </c>
     </row>
     <row r="67">
@@ -9295,7 +9295,7 @@
         <v>-0</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>-1.464</v>
+        <v>-1.463</v>
       </c>
     </row>
     <row r="68">
@@ -9313,7 +9313,7 @@
         </is>
       </c>
       <c r="D68" s="5" t="n">
-        <v>-0.235</v>
+        <v>-0.234</v>
       </c>
       <c r="E68" s="5" t="n">
         <v>0.745</v>
@@ -9328,7 +9328,7 @@
         <v>-0</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>-1.786</v>
+        <v>-1.785</v>
       </c>
     </row>
     <row r="69">
@@ -9361,7 +9361,7 @@
         <v>-0</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>-1.944</v>
+        <v>-1.943</v>
       </c>
     </row>
     <row r="70">
@@ -9415,7 +9415,7 @@
         <v>-0.299</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>0.745</v>
+        <v>0.744</v>
       </c>
       <c r="F71" s="5" t="n">
         <v>-0.309</v>
@@ -9427,7 +9427,7 @@
         <v>-0</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>-1.581</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="72">
@@ -9523,7 +9523,7 @@
         <v>-0</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I74" s="5" t="n">
         <v>-0</v>
@@ -9907,7 +9907,7 @@
         </is>
       </c>
       <c r="D86" s="5" t="n">
-        <v>0.152</v>
+        <v>0.151</v>
       </c>
       <c r="E86" s="5" t="n">
         <v>1.805</v>
@@ -9976,7 +9976,7 @@
         <v>0.113</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>1.5</v>
+        <v>1.501</v>
       </c>
       <c r="F88" s="5" t="n">
         <v>0.442</v>
@@ -10021,7 +10021,7 @@
         <v>0</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>0.591</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="90">
@@ -10045,7 +10045,7 @@
         <v>1.988</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.391</v>
+        <v>0.392</v>
       </c>
       <c r="G90" s="5" t="n">
         <v>0.287</v>
@@ -10054,7 +10054,7 @@
         <v>0</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>0.544</v>
+        <v>0.543</v>
       </c>
     </row>
     <row r="91">
@@ -10075,13 +10075,13 @@
         <v>0.048</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>1.497</v>
+        <v>1.498</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.305</v>
+        <v>0.306</v>
       </c>
       <c r="H91" s="5" t="n">
         <v>0</v>
@@ -10117,7 +10117,7 @@
         <v>0</v>
       </c>
       <c r="H92" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I92" s="5" t="n">
         <v>0</v>
@@ -10570,7 +10570,7 @@
         <v>0.146</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0.896</v>
+        <v>0.895</v>
       </c>
       <c r="F106" s="5" t="n">
         <v>-0.192</v>
@@ -10606,7 +10606,7 @@
         <v>1.941</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>-0.29</v>
+        <v>-0.291</v>
       </c>
       <c r="G107" s="5" t="n">
         <v>-0.248</v>
@@ -10639,7 +10639,7 @@
         <v>0.624</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>-0.322</v>
+        <v>-0.323</v>
       </c>
       <c r="G108" s="5" t="n">
         <v>-0.261</v>
@@ -10669,7 +10669,7 @@
         <v>0.19</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0.949</v>
+        <v>0.948</v>
       </c>
       <c r="F109" s="5" t="n">
         <v>-0.19</v>
@@ -10843,7 +10843,7 @@
         <v>-0</v>
       </c>
       <c r="H114" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I114" s="5" t="n">
         <v>0</v>
@@ -11104,7 +11104,7 @@
         <v>-0</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H122" s="5" t="n">
         <v>-0</v>
@@ -11137,7 +11137,7 @@
         <v>-0</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H123" s="5" t="n">
         <v>-0</v>
@@ -11275,7 +11275,7 @@
         <v>0</v>
       </c>
       <c r="I127" s="5" t="n">
-        <v>-0.542</v>
+        <v>-0.541</v>
       </c>
     </row>
     <row r="128">
@@ -11299,7 +11299,7 @@
         <v>1.415</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>0.324</v>
+        <v>0.325</v>
       </c>
       <c r="G128" s="5" t="n">
         <v>0.24</v>
@@ -11326,7 +11326,7 @@
         </is>
       </c>
       <c r="D129" s="5" t="n">
-        <v>-0.188</v>
+        <v>-0.187</v>
       </c>
       <c r="E129" s="5" t="n">
         <v>1.401</v>
@@ -11341,7 +11341,7 @@
         <v>0</v>
       </c>
       <c r="I129" s="5" t="n">
-        <v>-0.573</v>
+        <v>-0.572</v>
       </c>
     </row>
     <row r="130">
@@ -11365,7 +11365,7 @@
         <v>1.924</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>0.287</v>
+        <v>0.288</v>
       </c>
       <c r="G130" s="5" t="n">
         <v>0.223</v>
@@ -11395,10 +11395,10 @@
         <v>-0.111</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>1.41</v>
+        <v>1.411</v>
       </c>
       <c r="F131" s="5" t="n">
-        <v>0.32</v>
+        <v>0.321</v>
       </c>
       <c r="G131" s="5" t="n">
         <v>0.236</v>
@@ -11437,7 +11437,7 @@
         <v>0</v>
       </c>
       <c r="H132" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I132" s="5" t="n">
         <v>-0</v>
@@ -11599,7 +11599,7 @@
         <v>0</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H137" s="5" t="n">
         <v>-0</v>
@@ -11731,7 +11731,7 @@
         <v>0</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H141" s="5" t="n">
         <v>-0</v>
@@ -11797,7 +11797,7 @@
         <v>0</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H143" s="5" t="n">
         <v>-0</v>
@@ -11887,10 +11887,10 @@
         </is>
       </c>
       <c r="D146" s="5" t="n">
-        <v>-0.154</v>
+        <v>-0.153</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="F146" s="5" t="n">
         <v>-0.255</v>
@@ -11956,7 +11956,7 @@
         <v>-0.049</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>0.539</v>
+        <v>0.538</v>
       </c>
       <c r="F148" s="5" t="n">
         <v>-0.44</v>
@@ -12025,7 +12025,7 @@
         <v>1.878</v>
       </c>
       <c r="F150" s="5" t="n">
-        <v>-0.39</v>
+        <v>-0.391</v>
       </c>
       <c r="G150" s="5" t="n">
         <v>-0.309</v>
@@ -12055,13 +12055,13 @@
         <v>-0.113</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>0.542</v>
+        <v>0.541</v>
       </c>
       <c r="F151" s="5" t="n">
         <v>-0.436</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>-0.326</v>
+        <v>-0.327</v>
       </c>
       <c r="H151" s="5" t="n">
         <v>-0</v>
@@ -16522,7 +16522,7 @@
         <v>0</v>
       </c>
       <c r="I286" s="5" t="n">
-        <v>2.677</v>
+        <v>2.676</v>
       </c>
     </row>
     <row r="287">
@@ -16543,7 +16543,7 @@
         <v>0.34</v>
       </c>
       <c r="E287" s="5" t="n">
-        <v>2.189</v>
+        <v>2.188</v>
       </c>
       <c r="F287" s="5" t="n">
         <v>0.386</v>
@@ -16555,7 +16555,7 @@
         <v>0</v>
       </c>
       <c r="I287" s="5" t="n">
-        <v>1.691</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="288">
@@ -16588,7 +16588,7 @@
         <v>0</v>
       </c>
       <c r="I288" s="5" t="n">
-        <v>2.254</v>
+        <v>2.253</v>
       </c>
     </row>
     <row r="289">
@@ -16606,7 +16606,7 @@
         </is>
       </c>
       <c r="D289" s="5" t="n">
-        <v>0.903</v>
+        <v>0.902</v>
       </c>
       <c r="E289" s="5" t="n">
         <v>2.491</v>
@@ -16621,7 +16621,7 @@
         <v>0</v>
       </c>
       <c r="I289" s="5" t="n">
-        <v>2.721</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="290">
@@ -16654,7 +16654,7 @@
         <v>0</v>
       </c>
       <c r="I290" s="5" t="n">
-        <v>2.001</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291">
@@ -16687,7 +16687,7 @@
         <v>0</v>
       </c>
       <c r="I291" s="5" t="n">
-        <v>2.469</v>
+        <v>2.468</v>
       </c>
     </row>
     <row r="292">
@@ -17170,10 +17170,10 @@
         <v>0.697</v>
       </c>
       <c r="E306" s="5" t="n">
-        <v>2.052</v>
+        <v>2.051</v>
       </c>
       <c r="F306" s="5" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="G306" s="5" t="n">
         <v>0.006</v>
@@ -17182,7 +17182,7 @@
         <v>0</v>
       </c>
       <c r="I306" s="5" t="n">
-        <v>2.668</v>
+        <v>2.667</v>
       </c>
     </row>
     <row r="307">
@@ -17215,7 +17215,7 @@
         <v>0</v>
       </c>
       <c r="I307" s="5" t="n">
-        <v>1.69</v>
+        <v>1.689</v>
       </c>
     </row>
     <row r="308">
@@ -17248,7 +17248,7 @@
         <v>0</v>
       </c>
       <c r="I308" s="5" t="n">
-        <v>2.249</v>
+        <v>2.248</v>
       </c>
     </row>
     <row r="309">
@@ -17269,7 +17269,7 @@
         <v>0.899</v>
       </c>
       <c r="E309" s="5" t="n">
-        <v>2.109</v>
+        <v>2.108</v>
       </c>
       <c r="F309" s="5" t="n">
         <v>0.053</v>
@@ -17281,7 +17281,7 @@
         <v>0</v>
       </c>
       <c r="I309" s="5" t="n">
-        <v>2.712</v>
+        <v>2.711</v>
       </c>
     </row>
     <row r="310">
@@ -17314,7 +17314,7 @@
         <v>0</v>
       </c>
       <c r="I310" s="5" t="n">
-        <v>2</v>
+        <v>1.999</v>
       </c>
     </row>
     <row r="311">
@@ -17332,7 +17332,7 @@
         </is>
       </c>
       <c r="D311" s="5" t="n">
-        <v>0.34</v>
+        <v>0.339</v>
       </c>
       <c r="E311" s="5" t="n">
         <v>1.09</v>
@@ -17347,7 +17347,7 @@
         <v>-0</v>
       </c>
       <c r="I311" s="5" t="n">
-        <v>2.465</v>
+        <v>2.464</v>
       </c>
     </row>
     <row r="312">
@@ -17506,7 +17506,7 @@
         <v>-0</v>
       </c>
       <c r="G316" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H316" s="5" t="n">
         <v>0</v>
@@ -17539,7 +17539,7 @@
         <v>-0</v>
       </c>
       <c r="G317" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H317" s="5" t="n">
         <v>-0</v>
@@ -17572,7 +17572,7 @@
         <v>-0</v>
       </c>
       <c r="G318" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H318" s="5" t="n">
         <v>-0</v>
@@ -17605,7 +17605,7 @@
         <v>-0</v>
       </c>
       <c r="G319" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H319" s="5" t="n">
         <v>-0</v>
@@ -17704,7 +17704,7 @@
         <v>-0</v>
       </c>
       <c r="G322" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H322" s="5" t="n">
         <v>-0</v>
@@ -17737,7 +17737,7 @@
         <v>-0</v>
       </c>
       <c r="G323" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H323" s="5" t="n">
         <v>-0</v>
@@ -17827,22 +17827,22 @@
         </is>
       </c>
       <c r="D326" s="5" t="n">
-        <v>-0.7</v>
+        <v>-0.699</v>
       </c>
       <c r="E326" s="5" t="n">
-        <v>0.306</v>
+        <v>0.307</v>
       </c>
       <c r="F326" s="5" t="n">
         <v>-0.055</v>
       </c>
       <c r="G326" s="5" t="n">
-        <v>-0.031</v>
+        <v>-0.03</v>
       </c>
       <c r="H326" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I326" s="5" t="n">
-        <v>-2.663</v>
+        <v>-2.662</v>
       </c>
     </row>
     <row r="327">
@@ -17869,7 +17869,7 @@
         <v>-0.097</v>
       </c>
       <c r="G327" s="5" t="n">
-        <v>-0.047</v>
+        <v>-0.046</v>
       </c>
       <c r="H327" s="5" t="n">
         <v>-0</v>
@@ -17893,16 +17893,16 @@
         </is>
       </c>
       <c r="D328" s="5" t="n">
-        <v>-0.34</v>
+        <v>-0.339</v>
       </c>
       <c r="E328" s="5" t="n">
         <v>1.055</v>
       </c>
       <c r="F328" s="5" t="n">
-        <v>-0.113</v>
+        <v>-0.112</v>
       </c>
       <c r="G328" s="5" t="n">
-        <v>-0.053</v>
+        <v>-0.052</v>
       </c>
       <c r="H328" s="5" t="n">
         <v>0</v>
@@ -17929,10 +17929,10 @@
         <v>-0.897</v>
       </c>
       <c r="E329" s="5" t="n">
-        <v>0.358</v>
+        <v>0.359</v>
       </c>
       <c r="F329" s="5" t="n">
-        <v>-0.057</v>
+        <v>-0.056</v>
       </c>
       <c r="G329" s="5" t="n">
         <v>-0.032</v>
@@ -17941,7 +17941,7 @@
         <v>-0</v>
       </c>
       <c r="I329" s="5" t="n">
-        <v>-2.717</v>
+        <v>-2.716</v>
       </c>
     </row>
     <row r="330">
@@ -17974,7 +17974,7 @@
         <v>-0</v>
       </c>
       <c r="I330" s="5" t="n">
-        <v>-1.69</v>
+        <v>-1.689</v>
       </c>
     </row>
     <row r="331">
@@ -17995,7 +17995,7 @@
         <v>-0.407</v>
       </c>
       <c r="E331" s="5" t="n">
-        <v>1.05</v>
+        <v>1.051</v>
       </c>
       <c r="F331" s="5" t="n">
         <v>-0.116</v>
@@ -18007,7 +18007,7 @@
         <v>-0</v>
       </c>
       <c r="I331" s="5" t="n">
-        <v>-2.249</v>
+        <v>-2.248</v>
       </c>
     </row>
     <row r="332">
@@ -18166,7 +18166,7 @@
         <v>0</v>
       </c>
       <c r="G336" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H336" s="5" t="n">
         <v>0</v>
@@ -18199,7 +18199,7 @@
         <v>0</v>
       </c>
       <c r="G337" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H337" s="5" t="n">
         <v>-0</v>
@@ -18232,7 +18232,7 @@
         <v>0</v>
       </c>
       <c r="G338" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H338" s="5" t="n">
         <v>-0</v>
@@ -18265,7 +18265,7 @@
         <v>0</v>
       </c>
       <c r="G339" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H339" s="5" t="n">
         <v>-0</v>
@@ -18364,7 +18364,7 @@
         <v>0</v>
       </c>
       <c r="G342" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H342" s="5" t="n">
         <v>-0</v>
@@ -18397,7 +18397,7 @@
         <v>0</v>
       </c>
       <c r="G343" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H343" s="5" t="n">
         <v>-0</v>
@@ -18502,7 +18502,7 @@
         <v>-0</v>
       </c>
       <c r="I346" s="5" t="n">
-        <v>-2.672</v>
+        <v>-2.671</v>
       </c>
     </row>
     <row r="347">
@@ -18535,7 +18535,7 @@
         <v>-0</v>
       </c>
       <c r="I347" s="5" t="n">
-        <v>-2.001</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="348">
@@ -18568,7 +18568,7 @@
         <v>-0</v>
       </c>
       <c r="I348" s="5" t="n">
-        <v>-2.469</v>
+        <v>-2.468</v>
       </c>
     </row>
     <row r="349">
@@ -18601,7 +18601,7 @@
         <v>-0</v>
       </c>
       <c r="I349" s="5" t="n">
-        <v>-2.726</v>
+        <v>-2.725</v>
       </c>
     </row>
     <row r="350">
@@ -18634,7 +18634,7 @@
         <v>-0</v>
       </c>
       <c r="I350" s="5" t="n">
-        <v>-1.691</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="351">
@@ -18667,7 +18667,7 @@
         <v>-0</v>
       </c>
       <c r="I351" s="5" t="n">
-        <v>-2.254</v>
+        <v>-2.253</v>
       </c>
     </row>
     <row r="352">
@@ -18763,7 +18763,7 @@
         <v>-0</v>
       </c>
       <c r="H354" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I354" s="5" t="n">
         <v>-0</v>
@@ -19186,7 +19186,7 @@
         <v>2.107</v>
       </c>
       <c r="F367" s="5" t="n">
-        <v>0.553</v>
+        <v>0.554</v>
       </c>
       <c r="G367" s="5" t="n">
         <v>0.411</v>
@@ -19219,10 +19219,10 @@
         <v>1.745</v>
       </c>
       <c r="F368" s="5" t="n">
-        <v>0.619</v>
+        <v>0.62</v>
       </c>
       <c r="G368" s="5" t="n">
-        <v>0.436</v>
+        <v>0.437</v>
       </c>
       <c r="H368" s="5" t="n">
         <v>0</v>
@@ -19282,13 +19282,13 @@
         <v>0.041</v>
       </c>
       <c r="E370" s="5" t="n">
-        <v>2.106</v>
+        <v>2.107</v>
       </c>
       <c r="F370" s="5" t="n">
         <v>0.549</v>
       </c>
       <c r="G370" s="5" t="n">
-        <v>0.406</v>
+        <v>0.407</v>
       </c>
       <c r="H370" s="5" t="n">
         <v>0</v>
@@ -19315,10 +19315,10 @@
         <v>0.079</v>
       </c>
       <c r="E371" s="5" t="n">
-        <v>1.74</v>
+        <v>1.741</v>
       </c>
       <c r="F371" s="5" t="n">
-        <v>0.614</v>
+        <v>0.615</v>
       </c>
       <c r="G371" s="5" t="n">
         <v>0.432</v>
@@ -19846,10 +19846,10 @@
         <v>2.041</v>
       </c>
       <c r="F387" s="5" t="n">
-        <v>-0.407</v>
+        <v>-0.408</v>
       </c>
       <c r="G387" s="5" t="n">
-        <v>-0.344</v>
+        <v>-0.345</v>
       </c>
       <c r="H387" s="5" t="n">
         <v>-0</v>
@@ -19879,7 +19879,7 @@
         <v>0.516</v>
       </c>
       <c r="F388" s="5" t="n">
-        <v>-0.452</v>
+        <v>-0.453</v>
       </c>
       <c r="G388" s="5" t="n">
         <v>-0.362</v>
@@ -19888,7 +19888,7 @@
         <v>-0</v>
       </c>
       <c r="I388" s="5" t="n">
-        <v>0.593</v>
+        <v>0.592</v>
       </c>
     </row>
     <row r="389">
@@ -19921,7 +19921,7 @@
         <v>-0</v>
       </c>
       <c r="I389" s="5" t="n">
-        <v>0.798</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="390">
@@ -19975,10 +19975,10 @@
         <v>0.077</v>
       </c>
       <c r="E391" s="5" t="n">
-        <v>0.522</v>
+        <v>0.521</v>
       </c>
       <c r="F391" s="5" t="n">
-        <v>-0.446</v>
+        <v>-0.447</v>
       </c>
       <c r="G391" s="5" t="n">
         <v>-0.357</v>
@@ -20344,7 +20344,7 @@
         <v>-0</v>
       </c>
       <c r="G402" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H402" s="5" t="n">
         <v>-0</v>
@@ -20377,7 +20377,7 @@
         <v>-0</v>
       </c>
       <c r="G403" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H403" s="5" t="n">
         <v>-0</v>
@@ -20470,13 +20470,13 @@
         <v>-0.207</v>
       </c>
       <c r="E406" s="5" t="n">
-        <v>1.497</v>
+        <v>1.498</v>
       </c>
       <c r="F406" s="5" t="n">
         <v>0.266</v>
       </c>
       <c r="G406" s="5" t="n">
-        <v>0.267</v>
+        <v>0.268</v>
       </c>
       <c r="H406" s="5" t="n">
         <v>0</v>
@@ -20506,7 +20506,7 @@
         <v>2.017</v>
       </c>
       <c r="F407" s="5" t="n">
-        <v>0.408</v>
+        <v>0.409</v>
       </c>
       <c r="G407" s="5" t="n">
         <v>0.322</v>
@@ -20572,10 +20572,10 @@
         <v>1.551</v>
       </c>
       <c r="F409" s="5" t="n">
-        <v>0.262</v>
+        <v>0.263</v>
       </c>
       <c r="G409" s="5" t="n">
-        <v>0.263</v>
+        <v>0.264</v>
       </c>
       <c r="H409" s="5" t="n">
         <v>0</v>
@@ -20677,7 +20677,7 @@
         <v>0</v>
       </c>
       <c r="H412" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I412" s="5" t="n">
         <v>-0</v>
@@ -20839,7 +20839,7 @@
         <v>0</v>
       </c>
       <c r="G417" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H417" s="5" t="n">
         <v>-0</v>
@@ -20971,7 +20971,7 @@
         <v>0</v>
       </c>
       <c r="G421" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H421" s="5" t="n">
         <v>-0</v>
@@ -21037,7 +21037,7 @@
         <v>0</v>
       </c>
       <c r="G423" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H423" s="5" t="n">
         <v>-0</v>
@@ -21142,7 +21142,7 @@
         <v>-0</v>
       </c>
       <c r="I426" s="5" t="n">
-        <v>-0.8139999999999999</v>
+        <v>-0.8129999999999999</v>
       </c>
     </row>
     <row r="427">
@@ -21166,10 +21166,10 @@
         <v>1.951</v>
       </c>
       <c r="F427" s="5" t="n">
-        <v>-0.552</v>
+        <v>-0.553</v>
       </c>
       <c r="G427" s="5" t="n">
-        <v>-0.433</v>
+        <v>-0.434</v>
       </c>
       <c r="H427" s="5" t="n">
         <v>-0</v>
@@ -21193,22 +21193,22 @@
         </is>
       </c>
       <c r="D428" s="5" t="n">
-        <v>-0.08</v>
+        <v>-0.079</v>
       </c>
       <c r="E428" s="5" t="n">
         <v>0.396</v>
       </c>
       <c r="F428" s="5" t="n">
-        <v>-0.617</v>
+        <v>-0.618</v>
       </c>
       <c r="G428" s="5" t="n">
-        <v>-0.458</v>
+        <v>-0.459</v>
       </c>
       <c r="H428" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I428" s="5" t="n">
-        <v>-0.823</v>
+        <v>-0.822</v>
       </c>
     </row>
     <row r="429">
@@ -21235,7 +21235,7 @@
         <v>-0.354</v>
       </c>
       <c r="G429" s="5" t="n">
-        <v>-0.355</v>
+        <v>-0.356</v>
       </c>
       <c r="H429" s="5" t="n">
         <v>-0</v>
@@ -21787,7 +21787,7 @@
         </is>
       </c>
       <c r="D446" s="5" t="n">
-        <v>0.714</v>
+        <v>0.713</v>
       </c>
       <c r="E446" s="5" t="n">
         <v>2.29</v>
@@ -21802,7 +21802,7 @@
         <v>0</v>
       </c>
       <c r="I446" s="5" t="n">
-        <v>2.729</v>
+        <v>2.728</v>
       </c>
     </row>
     <row r="447">
@@ -21835,7 +21835,7 @@
         <v>0</v>
       </c>
       <c r="I447" s="5" t="n">
-        <v>1.749</v>
+        <v>1.748</v>
       </c>
     </row>
     <row r="448">
@@ -21868,7 +21868,7 @@
         <v>0</v>
       </c>
       <c r="I448" s="5" t="n">
-        <v>2.315</v>
+        <v>2.314</v>
       </c>
     </row>
     <row r="449">
@@ -21889,7 +21889,7 @@
         <v>0.92</v>
       </c>
       <c r="E449" s="5" t="n">
-        <v>2.34</v>
+        <v>2.339</v>
       </c>
       <c r="F449" s="5" t="n">
         <v>0.243</v>
@@ -21901,7 +21901,7 @@
         <v>0</v>
       </c>
       <c r="I449" s="5" t="n">
-        <v>2.775</v>
+        <v>2.774</v>
       </c>
     </row>
     <row r="450">
@@ -21934,7 +21934,7 @@
         <v>0</v>
       </c>
       <c r="I450" s="5" t="n">
-        <v>2.015</v>
+        <v>2.014</v>
       </c>
     </row>
     <row r="451">
@@ -21961,13 +21961,13 @@
         <v>0.445</v>
       </c>
       <c r="G451" s="5" t="n">
-        <v>0.276</v>
+        <v>0.277</v>
       </c>
       <c r="H451" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I451" s="5" t="n">
-        <v>2.5</v>
+        <v>2.499</v>
       </c>
     </row>
     <row r="452">
@@ -22462,7 +22462,7 @@
         <v>0</v>
       </c>
       <c r="I466" s="5" t="n">
-        <v>2.72</v>
+        <v>2.719</v>
       </c>
     </row>
     <row r="467">
@@ -22528,7 +22528,7 @@
         <v>-0</v>
       </c>
       <c r="I468" s="5" t="n">
-        <v>2.311</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="469">
@@ -22549,7 +22549,7 @@
         <v>0.917</v>
       </c>
       <c r="E469" s="5" t="n">
-        <v>1.95</v>
+        <v>1.949</v>
       </c>
       <c r="F469" s="5" t="n">
         <v>0.055</v>
@@ -22561,7 +22561,7 @@
         <v>0</v>
       </c>
       <c r="I469" s="5" t="n">
-        <v>2.766</v>
+        <v>2.765</v>
       </c>
     </row>
     <row r="470">
@@ -22579,13 +22579,13 @@
         </is>
       </c>
       <c r="D470" s="5" t="n">
-        <v>0.259</v>
+        <v>0.258</v>
       </c>
       <c r="E470" s="5" t="n">
         <v>1.882</v>
       </c>
       <c r="F470" s="5" t="n">
-        <v>0.103</v>
+        <v>0.102</v>
       </c>
       <c r="G470" s="5" t="n">
         <v>0.028</v>
@@ -22594,7 +22594,7 @@
         <v>0</v>
       </c>
       <c r="I470" s="5" t="n">
-        <v>2.014</v>
+        <v>2.013</v>
       </c>
     </row>
     <row r="471">
@@ -22615,7 +22615,7 @@
         <v>0.352</v>
       </c>
       <c r="E471" s="5" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="F471" s="5" t="n">
         <v>0.12</v>
@@ -22627,7 +22627,7 @@
         <v>-0</v>
       </c>
       <c r="I471" s="5" t="n">
-        <v>2.495</v>
+        <v>2.494</v>
       </c>
     </row>
     <row r="472">
@@ -22786,7 +22786,7 @@
         <v>-0</v>
       </c>
       <c r="G476" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H476" s="5" t="n">
         <v>0</v>
@@ -22819,7 +22819,7 @@
         <v>-0</v>
       </c>
       <c r="G477" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H477" s="5" t="n">
         <v>-0</v>
@@ -22852,7 +22852,7 @@
         <v>-0</v>
       </c>
       <c r="G478" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H478" s="5" t="n">
         <v>-0</v>
@@ -22885,7 +22885,7 @@
         <v>-0</v>
       </c>
       <c r="G479" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H479" s="5" t="n">
         <v>-0</v>
@@ -22984,7 +22984,7 @@
         <v>-0</v>
       </c>
       <c r="G482" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H482" s="5" t="n">
         <v>-0</v>
@@ -23017,7 +23017,7 @@
         <v>-0</v>
       </c>
       <c r="G483" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H483" s="5" t="n">
         <v>-0</v>
@@ -23113,7 +23113,7 @@
         <v>0.121</v>
       </c>
       <c r="F486" s="5" t="n">
-        <v>-0.056</v>
+        <v>-0.055</v>
       </c>
       <c r="G486" s="5" t="n">
         <v>-0.029</v>
@@ -23122,7 +23122,7 @@
         <v>-0</v>
       </c>
       <c r="I486" s="5" t="n">
-        <v>-2.716</v>
+        <v>-2.715</v>
       </c>
     </row>
     <row r="487">
@@ -23140,7 +23140,7 @@
         </is>
       </c>
       <c r="D487" s="5" t="n">
-        <v>-0.259</v>
+        <v>-0.258</v>
       </c>
       <c r="E487" s="5" t="n">
         <v>1.597</v>
@@ -23149,7 +23149,7 @@
         <v>-0.099</v>
       </c>
       <c r="G487" s="5" t="n">
-        <v>-0.046</v>
+        <v>-0.045</v>
       </c>
       <c r="H487" s="5" t="n">
         <v>-0</v>
@@ -23176,7 +23176,7 @@
         <v>-0.352</v>
       </c>
       <c r="E488" s="5" t="n">
-        <v>0.901</v>
+        <v>0.902</v>
       </c>
       <c r="F488" s="5" t="n">
         <v>-0.115</v>
@@ -23188,7 +23188,7 @@
         <v>0</v>
       </c>
       <c r="I488" s="5" t="n">
-        <v>-2.495</v>
+        <v>-2.494</v>
       </c>
     </row>
     <row r="489">
@@ -23206,7 +23206,7 @@
         </is>
       </c>
       <c r="D489" s="5" t="n">
-        <v>-0.915</v>
+        <v>-0.914</v>
       </c>
       <c r="E489" s="5" t="n">
         <v>0.165</v>
@@ -23221,7 +23221,7 @@
         <v>-0</v>
       </c>
       <c r="I489" s="5" t="n">
-        <v>-2.769</v>
+        <v>-2.768</v>
       </c>
     </row>
     <row r="490">
@@ -23287,7 +23287,7 @@
         <v>0</v>
       </c>
       <c r="I491" s="5" t="n">
-        <v>-2.311</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="492">
@@ -23446,7 +23446,7 @@
         <v>0</v>
       </c>
       <c r="G496" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H496" s="5" t="n">
         <v>0</v>
@@ -23479,7 +23479,7 @@
         <v>0</v>
       </c>
       <c r="G497" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H497" s="5" t="n">
         <v>-0</v>
@@ -23512,7 +23512,7 @@
         <v>0</v>
       </c>
       <c r="G498" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H498" s="5" t="n">
         <v>-0</v>
@@ -23545,7 +23545,7 @@
         <v>0</v>
       </c>
       <c r="G499" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H499" s="5" t="n">
         <v>-0</v>
@@ -23644,7 +23644,7 @@
         <v>0</v>
       </c>
       <c r="G502" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H502" s="5" t="n">
         <v>-0</v>
@@ -23677,7 +23677,7 @@
         <v>0</v>
       </c>
       <c r="G503" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H503" s="5" t="n">
         <v>-0</v>
@@ -23767,7 +23767,7 @@
         </is>
       </c>
       <c r="D506" s="5" t="n">
-        <v>-0.716</v>
+        <v>-0.715</v>
       </c>
       <c r="E506" s="5" t="n">
         <v>-0.269</v>
@@ -23782,7 +23782,7 @@
         <v>-0</v>
       </c>
       <c r="I506" s="5" t="n">
-        <v>-2.725</v>
+        <v>-2.724</v>
       </c>
     </row>
     <row r="507">
@@ -23815,7 +23815,7 @@
         <v>-0</v>
       </c>
       <c r="I507" s="5" t="n">
-        <v>-2.015</v>
+        <v>-2.014</v>
       </c>
     </row>
     <row r="508">
@@ -23833,10 +23833,10 @@
         </is>
       </c>
       <c r="D508" s="5" t="n">
-        <v>-0.353</v>
+        <v>-0.352</v>
       </c>
       <c r="E508" s="5" t="n">
-        <v>0.526</v>
+        <v>0.525</v>
       </c>
       <c r="F508" s="5" t="n">
         <v>-0.443</v>
@@ -23848,7 +23848,7 @@
         <v>-0</v>
       </c>
       <c r="I508" s="5" t="n">
-        <v>-2.5</v>
+        <v>-2.499</v>
       </c>
     </row>
     <row r="509">
@@ -23881,7 +23881,7 @@
         <v>-0</v>
       </c>
       <c r="I509" s="5" t="n">
-        <v>-2.779</v>
+        <v>-2.778</v>
       </c>
     </row>
     <row r="510">
@@ -23914,7 +23914,7 @@
         <v>-0</v>
       </c>
       <c r="I510" s="5" t="n">
-        <v>-1.749</v>
+        <v>-1.748</v>
       </c>
     </row>
     <row r="511">
@@ -23932,7 +23932,7 @@
         </is>
       </c>
       <c r="D511" s="5" t="n">
-        <v>-0.411</v>
+        <v>-0.41</v>
       </c>
       <c r="E511" s="5" t="n">
         <v>0.524</v>
@@ -23947,7 +23947,7 @@
         <v>-0</v>
       </c>
       <c r="I511" s="5" t="n">
-        <v>-2.315</v>
+        <v>-2.314</v>
       </c>
     </row>
     <row r="512">
@@ -24430,13 +24430,13 @@
         <v>0.217</v>
       </c>
       <c r="E526" s="5" t="n">
-        <v>1.986</v>
+        <v>1.987</v>
       </c>
       <c r="F526" s="5" t="n">
         <v>0.361</v>
       </c>
       <c r="G526" s="5" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="H526" s="5" t="n">
         <v>0</v>
@@ -24496,10 +24496,10 @@
         <v>0.145</v>
       </c>
       <c r="E528" s="5" t="n">
-        <v>1.605</v>
+        <v>1.606</v>
       </c>
       <c r="F528" s="5" t="n">
-        <v>0.631</v>
+        <v>0.632</v>
       </c>
       <c r="G528" s="5" t="n">
         <v>0.447</v>
@@ -24508,7 +24508,7 @@
         <v>0</v>
       </c>
       <c r="I528" s="5" t="n">
-        <v>0.637</v>
+        <v>0.636</v>
       </c>
     </row>
     <row r="529">
@@ -24529,7 +24529,7 @@
         <v>0.282</v>
       </c>
       <c r="E529" s="5" t="n">
-        <v>2.033</v>
+        <v>2.034</v>
       </c>
       <c r="F529" s="5" t="n">
         <v>0.358</v>
@@ -24541,7 +24541,7 @@
         <v>0</v>
       </c>
       <c r="I529" s="5" t="n">
-        <v>0.846</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="530">
@@ -24565,10 +24565,10 @@
         <v>1.818</v>
       </c>
       <c r="F530" s="5" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G530" s="5" t="n">
-        <v>0.416</v>
+        <v>0.417</v>
       </c>
       <c r="H530" s="5" t="n">
         <v>0</v>
@@ -24598,10 +24598,10 @@
         <v>1.601</v>
       </c>
       <c r="F531" s="5" t="n">
-        <v>0.626</v>
+        <v>0.627</v>
       </c>
       <c r="G531" s="5" t="n">
-        <v>0.442</v>
+        <v>0.443</v>
       </c>
       <c r="H531" s="5" t="n">
         <v>0</v>
@@ -25090,13 +25090,13 @@
         <v>0.209</v>
       </c>
       <c r="E546" s="5" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F546" s="5" t="n">
         <v>-0.274</v>
       </c>
       <c r="G546" s="5" t="n">
-        <v>-0.295</v>
+        <v>-0.296</v>
       </c>
       <c r="H546" s="5" t="n">
         <v>-0</v>
@@ -25126,10 +25126,10 @@
         <v>1.752</v>
       </c>
       <c r="F547" s="5" t="n">
-        <v>-0.415</v>
+        <v>-0.416</v>
       </c>
       <c r="G547" s="5" t="n">
-        <v>-0.349</v>
+        <v>-0.35</v>
       </c>
       <c r="H547" s="5" t="n">
         <v>-0</v>
@@ -25159,7 +25159,7 @@
         <v>0.352</v>
       </c>
       <c r="F548" s="5" t="n">
-        <v>-0.461</v>
+        <v>-0.462</v>
       </c>
       <c r="G548" s="5" t="n">
         <v>-0.367</v>
@@ -25189,13 +25189,13 @@
         <v>0.271</v>
       </c>
       <c r="E549" s="5" t="n">
-        <v>0.734</v>
+        <v>0.733</v>
       </c>
       <c r="F549" s="5" t="n">
-        <v>-0.27</v>
+        <v>-0.271</v>
       </c>
       <c r="G549" s="5" t="n">
-        <v>-0.291</v>
+        <v>-0.292</v>
       </c>
       <c r="H549" s="5" t="n">
         <v>-0</v>
@@ -25222,13 +25222,13 @@
         <v>0.049</v>
       </c>
       <c r="E550" s="5" t="n">
-        <v>1.753</v>
+        <v>1.752</v>
       </c>
       <c r="F550" s="5" t="n">
         <v>-0.41</v>
       </c>
       <c r="G550" s="5" t="n">
-        <v>-0.344</v>
+        <v>-0.345</v>
       </c>
       <c r="H550" s="5" t="n">
         <v>-0</v>
@@ -25258,7 +25258,7 @@
         <v>0.358</v>
       </c>
       <c r="F551" s="5" t="n">
-        <v>-0.455</v>
+        <v>-0.456</v>
       </c>
       <c r="G551" s="5" t="n">
         <v>-0.362</v>
@@ -25267,7 +25267,7 @@
         <v>-0</v>
       </c>
       <c r="I551" s="5" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="552">
@@ -25624,7 +25624,7 @@
         <v>-0</v>
       </c>
       <c r="G562" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H562" s="5" t="n">
         <v>-0</v>
@@ -25657,7 +25657,7 @@
         <v>-0</v>
       </c>
       <c r="G563" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H563" s="5" t="n">
         <v>-0</v>
@@ -25750,10 +25750,10 @@
         <v>-0.211</v>
       </c>
       <c r="E566" s="5" t="n">
-        <v>1.335</v>
+        <v>1.336</v>
       </c>
       <c r="F566" s="5" t="n">
-        <v>0.271</v>
+        <v>0.272</v>
       </c>
       <c r="G566" s="5" t="n">
         <v>0.275</v>
@@ -25786,7 +25786,7 @@
         <v>1.727</v>
       </c>
       <c r="F567" s="5" t="n">
-        <v>0.416</v>
+        <v>0.417</v>
       </c>
       <c r="G567" s="5" t="n">
         <v>0.33</v>
@@ -25819,10 +25819,10 @@
         <v>1.483</v>
       </c>
       <c r="F568" s="5" t="n">
-        <v>0.463</v>
+        <v>0.464</v>
       </c>
       <c r="G568" s="5" t="n">
-        <v>0.348</v>
+        <v>0.349</v>
       </c>
       <c r="H568" s="5" t="n">
         <v>0</v>
@@ -25855,13 +25855,13 @@
         <v>0.268</v>
       </c>
       <c r="G569" s="5" t="n">
-        <v>0.27</v>
+        <v>0.271</v>
       </c>
       <c r="H569" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I569" s="5" t="n">
-        <v>-0.8179999999999999</v>
+        <v>-0.8169999999999999</v>
       </c>
     </row>
     <row r="570">
@@ -25918,7 +25918,7 @@
         <v>1.477</v>
       </c>
       <c r="F571" s="5" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="G571" s="5" t="n">
         <v>0.343</v>
@@ -25957,7 +25957,7 @@
         <v>0</v>
       </c>
       <c r="H572" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I572" s="5" t="n">
         <v>-0</v>
@@ -26119,7 +26119,7 @@
         <v>0</v>
       </c>
       <c r="G577" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H577" s="5" t="n">
         <v>-0</v>
@@ -26251,7 +26251,7 @@
         <v>0</v>
       </c>
       <c r="G581" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H581" s="5" t="n">
         <v>-0</v>
@@ -26317,7 +26317,7 @@
         <v>0</v>
       </c>
       <c r="G583" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H583" s="5" t="n">
         <v>-0</v>
@@ -26410,7 +26410,7 @@
         <v>-0.219</v>
       </c>
       <c r="E586" s="5" t="n">
-        <v>0.035</v>
+        <v>0.034</v>
       </c>
       <c r="F586" s="5" t="n">
         <v>-0.364</v>
@@ -26446,7 +26446,7 @@
         <v>1.66</v>
       </c>
       <c r="F587" s="5" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="G587" s="5" t="n">
         <v>-0.44</v>
@@ -26476,10 +26476,10 @@
         <v>-0.08699999999999999</v>
       </c>
       <c r="E588" s="5" t="n">
-        <v>0.23</v>
+        <v>0.229</v>
       </c>
       <c r="F588" s="5" t="n">
-        <v>-0.629</v>
+        <v>-0.63</v>
       </c>
       <c r="G588" s="5" t="n">
         <v>-0.466</v>
@@ -26506,7 +26506,7 @@
         </is>
       </c>
       <c r="D589" s="5" t="n">
-        <v>-0.28</v>
+        <v>-0.279</v>
       </c>
       <c r="E589" s="5" t="n">
         <v>0.081</v>
@@ -26515,7 +26515,7 @@
         <v>-0.361</v>
       </c>
       <c r="G589" s="5" t="n">
-        <v>-0.36</v>
+        <v>-0.361</v>
       </c>
       <c r="H589" s="5" t="n">
         <v>-0</v>
@@ -26578,16 +26578,16 @@
         <v>0.234</v>
       </c>
       <c r="F591" s="5" t="n">
-        <v>-0.624</v>
+        <v>-0.625</v>
       </c>
       <c r="G591" s="5" t="n">
-        <v>-0.461</v>
+        <v>-0.462</v>
       </c>
       <c r="H591" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="I591" s="5" t="n">
-        <v>-0.637</v>
+        <v>-0.636</v>
       </c>
     </row>
     <row r="592">
@@ -34423,7 +34423,7 @@
         <v>23</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G54" s="10" t="n">
         <v>16</v>
@@ -34597,7 +34597,7 @@
         <v>27</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="61">
@@ -34765,7 +34765,7 @@
         <v>24</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67">
@@ -34815,7 +34815,7 @@
         <v>20</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G68" s="10" t="n">
         <v>24</v>
@@ -34871,7 +34871,7 @@
         <v>23</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G70" s="10" t="n">
         <v>25</v>
@@ -34927,7 +34927,7 @@
         <v>20</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G72" s="10" t="n">
         <v>24</v>
@@ -34983,7 +34983,7 @@
         <v>23</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G74" s="10" t="n">
         <v>25</v>
@@ -35039,7 +35039,7 @@
         <v>20</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G76" s="10" t="n">
         <v>26</v>
@@ -35095,7 +35095,7 @@
         <v>23</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G78" s="10" t="n">
         <v>27</v>
@@ -35675,7 +35675,7 @@
         <v>-1.518</v>
       </c>
       <c r="E100" s="9" t="n">
-        <v>-0.629</v>
+        <v>-0.63</v>
       </c>
       <c r="F100" s="9" t="n">
         <v>-0.72</v>
@@ -36155,7 +36155,7 @@
         <v>57</v>
       </c>
       <c r="G117" s="10" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H117" s="10" t="n">
         <v>45</v>
@@ -36323,7 +36323,7 @@
         <v>46</v>
       </c>
       <c r="G123" s="10" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="H123" s="10" t="n">
         <v>51</v>
@@ -36656,7 +36656,7 @@
         <v>46</v>
       </c>
       <c r="F135" s="10" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G135" s="10" t="n">
         <v>51</v>
@@ -36712,7 +36712,7 @@
         <v>49</v>
       </c>
       <c r="F137" s="10" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G137" s="10" t="n">
         <v>34</v>
@@ -36886,7 +36886,7 @@
         <v>57</v>
       </c>
       <c r="H143" s="10" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="144">
@@ -37104,7 +37104,7 @@
         <v>46</v>
       </c>
       <c r="F151" s="10" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="G151" s="10" t="n">
         <v>51</v>
@@ -37160,7 +37160,7 @@
         <v>49</v>
       </c>
       <c r="F153" s="10" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G153" s="10" t="n">
         <v>53</v>
@@ -37216,7 +37216,7 @@
         <v>46</v>
       </c>
       <c r="F155" s="10" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="G155" s="10" t="n">
         <v>51</v>
@@ -37272,7 +37272,7 @@
         <v>49</v>
       </c>
       <c r="F157" s="10" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G157" s="10" t="n">
         <v>53</v>
@@ -37328,7 +37328,7 @@
         <v>46</v>
       </c>
       <c r="F159" s="10" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G159" s="10" t="n">
         <v>55</v>
@@ -37384,7 +37384,7 @@
         <v>49</v>
       </c>
       <c r="F161" s="10" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G161" s="10" t="n">
         <v>57</v>
